--- a/files/recipe_052026.xlsx
+++ b/files/recipe_052026.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Drink" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Food" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="261">
   <si>
     <t>Lemonade by Lemonica recipe</t>
   </si>
@@ -49,499 +50,751 @@
     <t>Ambient</t>
   </si>
   <si>
+    <t>Granulated sugar</t>
+  </si>
+  <si>
+    <t>6kg</t>
+  </si>
+  <si>
+    <t>1. Add 6kg of sugar into a clean preparation container.</t>
+  </si>
+  <si>
+    <t>Hot Water</t>
+  </si>
+  <si>
+    <t>3400ml</t>
+  </si>
+  <si>
+    <t>2. Boil 3400ml of water.</t>
+  </si>
+  <si>
+    <t>3. Pour the hot water into the sugar carefully.</t>
+  </si>
+  <si>
+    <t>4. Mix thoroughly until all sugar is fully dissolved.</t>
+  </si>
+  <si>
+    <t>London Shot</t>
+  </si>
+  <si>
+    <t>10 Days</t>
+  </si>
+  <si>
+    <t>Fridge</t>
+  </si>
+  <si>
+    <t>3400g</t>
+  </si>
+  <si>
+    <t>1. Add Mojito Syrup into a clean preparation container.</t>
+  </si>
+  <si>
+    <t>Whole Shot</t>
+  </si>
+  <si>
+    <t>1P (1905g)</t>
+  </si>
+  <si>
+    <t>2. Add 1 pack of Whole Shot.</t>
+  </si>
+  <si>
+    <t>3. Mix evenly until fully combined.</t>
+  </si>
+  <si>
+    <t>Prep Shot</t>
+  </si>
+  <si>
+    <t>5200g</t>
+  </si>
+  <si>
+    <t>1. Pour London Shot into a clean container.</t>
+  </si>
+  <si>
+    <t>Fresh Lemon</t>
+  </si>
+  <si>
+    <t>250g</t>
+  </si>
+  <si>
+    <t>2. Add freshly squeezed lemon juice.</t>
+  </si>
+  <si>
+    <t>3. Mix thoroughly until evenly combined.</t>
+  </si>
+  <si>
+    <t>4. Store refrigerated.</t>
+  </si>
+  <si>
+    <t>Ultra Shot</t>
+  </si>
+  <si>
+    <t>1200g</t>
+  </si>
+  <si>
+    <t>1. Add Prep Shot into a clean container.</t>
+  </si>
+  <si>
+    <t>Citric Acid</t>
+  </si>
+  <si>
+    <t>100g</t>
+  </si>
+  <si>
+    <t>2. Add citric acid.</t>
+  </si>
+  <si>
+    <t>3. Mix thoroughly until fully dissolved.</t>
+  </si>
+  <si>
+    <t>Original Lemonade</t>
+  </si>
+  <si>
+    <t>72 Hours</t>
+  </si>
+  <si>
+    <t>1. Add Prep Shot into a preparation container.</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>2400g</t>
+  </si>
+  <si>
+    <t>2. Add water.</t>
+  </si>
+  <si>
+    <t>3. Close the lid and shake well until fully combined.</t>
+  </si>
+  <si>
+    <t>Iced Tea</t>
+  </si>
+  <si>
+    <t>12 Hours</t>
+  </si>
+  <si>
+    <t>Tea Packs</t>
+  </si>
+  <si>
+    <t>4 pcs</t>
+  </si>
+  <si>
+    <t>1. Add tea packs into hot water.</t>
+  </si>
+  <si>
+    <t>1500ml</t>
+  </si>
+  <si>
+    <t>2. Brew for 3 minutes.</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>500g</t>
+  </si>
+  <si>
+    <t>3. Remove all tea packs.</t>
+  </si>
+  <si>
+    <t>4. Add ice immediately and stir well.</t>
+  </si>
+  <si>
+    <t>Fresh Fruit</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>1/6 slice</t>
+  </si>
+  <si>
+    <t>1. Wash all fruits thoroughly before preparation.</t>
+  </si>
+  <si>
+    <t>Strawberry</t>
+  </si>
+  <si>
+    <t>Quarter cut</t>
+  </si>
+  <si>
+    <t>2. Cut the fruits accourding the size</t>
+  </si>
+  <si>
+    <t>Blueberry</t>
+  </si>
+  <si>
+    <t>No cutting required</t>
+  </si>
+  <si>
+    <t>Always wear gloves when handling fresh fruits.</t>
+  </si>
+  <si>
+    <t>Strawberry source</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen strawberry </t>
+  </si>
+  <si>
+    <t>1000g*5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Defrost strawberries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar </t>
+  </si>
+  <si>
+    <t>1750g</t>
+  </si>
+  <si>
+    <t>2. Put 1kg of strawberries in a blender</t>
+  </si>
+  <si>
+    <t>3. Put strawberries and sugar into a pot</t>
+  </si>
+  <si>
+    <t>4. Heat to 2000°, stirring continuously for 20 min</t>
+  </si>
+  <si>
+    <t>5. Place the sauce in an ice bath and stir for 10 min</t>
+  </si>
+  <si>
+    <t>6. Pack them</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Classic</t>
+  </si>
+  <si>
+    <t>Medium (16oz)</t>
+  </si>
+  <si>
+    <t>150g</t>
+  </si>
+  <si>
+    <t>1. Add 150g of ice into a Medium (16oz) cup.</t>
+  </si>
+  <si>
+    <t>300g</t>
+  </si>
+  <si>
+    <t>2. Pour 300g of prepared Original Lemonade</t>
+  </si>
+  <si>
+    <t>Large (24oz)</t>
+  </si>
+  <si>
+    <t>180g</t>
+  </si>
+  <si>
+    <t>1. Add 180g of ice into a Large (24oz) cup.</t>
+  </si>
+  <si>
+    <t>400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pour 400g of prepared Original Lemonade </t>
+  </si>
+  <si>
+    <t>Fizzy Lemonade</t>
+  </si>
+  <si>
+    <t>70g</t>
+  </si>
+  <si>
+    <t>2. Add 60ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>Sparkling Water</t>
+  </si>
+  <si>
+    <t>240g</t>
+  </si>
+  <si>
+    <t>3. Pour sparkling water and stir well.</t>
+  </si>
+  <si>
+    <t>89g</t>
+  </si>
+  <si>
+    <t>2. Add 15ml and 60ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>Ultra Lemonade</t>
+  </si>
+  <si>
+    <t>2. Add 60ml ladle of Ultra Shot.</t>
+  </si>
+  <si>
+    <t>2. Add 15ml and 60ml ladle of Ultra Shot.</t>
+  </si>
+  <si>
+    <t>Hot</t>
+  </si>
+  <si>
+    <t>Hot Lemonade</t>
+  </si>
+  <si>
+    <t>35g</t>
+  </si>
+  <si>
+    <t>1. Add 65g of Prep Shot into a Medium cup.</t>
+  </si>
+  <si>
+    <t>2. Pour hot water and stir well.</t>
+  </si>
+  <si>
+    <t>Flavor</t>
+  </si>
+  <si>
+    <t>Triple Lemonade</t>
+  </si>
+  <si>
+    <t>2. Add 30ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>50g</t>
+  </si>
+  <si>
+    <t>3. Add fresh lemon juice.</t>
+  </si>
+  <si>
+    <t>4. Pour sparkling water and stir well.</t>
+  </si>
+  <si>
+    <t>Cola Lemonade</t>
+  </si>
+  <si>
+    <t>2. Add 65g of Prep Shot.</t>
+  </si>
+  <si>
+    <t>Cola</t>
+  </si>
+  <si>
+    <t>3. Pour cola and stir well.</t>
+  </si>
+  <si>
+    <t>Fruits&amp;Fizzy (L)</t>
+  </si>
+  <si>
+    <t>Fruits</t>
+  </si>
+  <si>
+    <t>1. Add fruits into a Large (24oz) cup and smash fruits</t>
+  </si>
+  <si>
+    <t>2. Add 180g of ice into a Medium (16oz) cup.</t>
+  </si>
+  <si>
+    <t>Prep shot</t>
+  </si>
+  <si>
+    <t>3. Add 15ml and 60ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>Sparkling</t>
+  </si>
+  <si>
+    <t>Fruits&amp;Tea (L)</t>
+  </si>
+  <si>
+    <t>4. Pour tea and stir well.</t>
+  </si>
+  <si>
+    <t>Strawberry Frozen Lemonade</t>
+  </si>
+  <si>
+    <t>230g</t>
+  </si>
+  <si>
+    <t>1. Add 230g of ice and 40g of water into a blender cup.</t>
+  </si>
+  <si>
+    <t>40g</t>
+  </si>
+  <si>
+    <t>3. Add 65g of strawberry.</t>
+  </si>
+  <si>
+    <t>65g</t>
+  </si>
+  <si>
+    <t>4. Blend for approximately 20 seconds until smooth.</t>
+  </si>
+  <si>
+    <t>Blueberry Frozen Lemonade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Add 65g of blueberries </t>
+  </si>
+  <si>
+    <t>Kiwi Frozen Lemonade</t>
+  </si>
+  <si>
+    <t>104g</t>
+  </si>
+  <si>
+    <t>3. Add 65g of kiwi</t>
+  </si>
+  <si>
+    <t>Matcha</t>
+  </si>
+  <si>
+    <t>Matcha Lemonade</t>
+  </si>
+  <si>
+    <t>54g</t>
+  </si>
+  <si>
+    <t>2. Add 2 30ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>3. Add 240g of water and stir well</t>
+  </si>
+  <si>
+    <t>Matcha Powder</t>
+  </si>
+  <si>
+    <t>2g</t>
+  </si>
+  <si>
+    <t>4. Add 2g of matcha powder and 50g of hot water into matcha bowl</t>
+  </si>
+  <si>
+    <t>Hot water</t>
+  </si>
+  <si>
+    <t>5. Whisk the matcha thoroughly until smooth and formy</t>
+  </si>
+  <si>
+    <t>6. Pour the prepared matcha onto the ice lemonade base</t>
+  </si>
+  <si>
+    <t>2. Add 15ml and 30ml ladle of Prep Shot.</t>
+  </si>
+  <si>
+    <t>3g</t>
+  </si>
+  <si>
+    <t>4. Add matcha powder and hot water into matcha bowl</t>
+  </si>
+  <si>
+    <t>Strawberry Matcha Lemonade</t>
+  </si>
+  <si>
+    <t>Strawberry Sauce</t>
+  </si>
+  <si>
+    <t>1. Add strawberry sauce into a Medium (16oz) cup.</t>
+  </si>
+  <si>
+    <t>2. Add 150g of ice</t>
+  </si>
+  <si>
+    <t>Original Lemonade Base</t>
+  </si>
+  <si>
+    <t>3. Add 230g of Original Lemonade Base.</t>
+  </si>
+  <si>
+    <t>Mango Matcha Lemonade</t>
+  </si>
+  <si>
+    <t>Mango Puree</t>
+  </si>
+  <si>
+    <t>1. Add 2 pomp of mango purée into a Medium (16oz) cup.</t>
+  </si>
+  <si>
+    <t>Topping</t>
+  </si>
+  <si>
+    <t>Extra lemon</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.5 P</t>
+  </si>
+  <si>
+    <t>1. Squeeze fresh lemons using the lemon squeezer.</t>
+  </si>
+  <si>
+    <t>2. Add 35ml of fresh lemon juice.</t>
+  </si>
+  <si>
+    <t>Smash Fruits</t>
+  </si>
+  <si>
+    <t>Fresh fruits</t>
+  </si>
+  <si>
+    <t>1. Pour the fruits and smash</t>
+  </si>
+  <si>
+    <t>Lemonade by Lemonica recipe (food)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category </t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparation </t>
+  </si>
+  <si>
+    <t>Whipped Cream</t>
+  </si>
+  <si>
+    <t>Double cream</t>
+  </si>
+  <si>
+    <t>950g</t>
+  </si>
+  <si>
+    <t>1. Add all ingredients into the mixer and mix thoroughly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granulated sugar </t>
+  </si>
+  <si>
+    <t>190g</t>
+  </si>
+  <si>
+    <t>2. Using a spatula, transfer the whipped cream into a piping bag.</t>
+  </si>
+  <si>
+    <t>Matcha Whipped Cream</t>
+  </si>
+  <si>
+    <t>Matcha powder</t>
+  </si>
+  <si>
+    <t>12g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strawberry </t>
+  </si>
+  <si>
+    <t>600g</t>
+  </si>
+  <si>
+    <t>White bread</t>
+  </si>
+  <si>
+    <t>Hovis soft white Thick</t>
+  </si>
+  <si>
+    <t>1 pack</t>
+  </si>
+  <si>
+    <t>Life shelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruits Sandwich </t>
+  </si>
+  <si>
+    <t>Strawberry Sandwich (Yield 12p)</t>
+  </si>
+  <si>
+    <t>48h</t>
+  </si>
+  <si>
+    <t>1. Remove the stems from the strawberries and remove any dirt.</t>
+  </si>
+  <si>
+    <t>2. Place the strawberries stem-side down to drain excess moisture.</t>
+  </si>
+  <si>
+    <t>3. Cut off the top and bottom crust of the bread.</t>
+  </si>
+  <si>
+    <t>4. Add 50g of whipped cream onto the bread.</t>
+  </si>
+  <si>
+    <t>5. Place 3 large strawberries diagonally across the bread.</t>
+  </si>
+  <si>
+    <t>6. Place 1 small strawberry on each opposite corner.</t>
+  </si>
+  <si>
+    <t>7. Add 150g of whipped cream and fully cover the strawberries.</t>
+  </si>
+  <si>
+    <t>8. Place the second bread slice on top, align straight, and flip the sandwich upside down.</t>
+  </si>
+  <si>
+    <t>9. Store in the fridge for approximately 5–10 minutes to allow the cream to stabilise.</t>
+  </si>
+  <si>
+    <t>10. Cut in half and pack properly.</t>
+  </si>
+  <si>
+    <t>Strawberry Matcha Sandwich (Yield 12p)</t>
+  </si>
+  <si>
+    <t>4. Add 50g of matcha whipped cream onto the bread.</t>
+  </si>
+  <si>
+    <t>Crepe Mixture (Total 2100-2200g)</t>
+  </si>
+  <si>
+    <t>McDougalls Pre-Sifted Plain Flour</t>
+  </si>
+  <si>
+    <t>1. Mix all flour, salt, sugar, and matcha powder together.</t>
+  </si>
+  <si>
+    <t>Salt</t>
+  </si>
+  <si>
+    <t>10g</t>
+  </si>
+  <si>
+    <t>2. Mix the milk, water and eggs together.</t>
+  </si>
+  <si>
     <t>Sugar</t>
   </si>
   <si>
-    <t>6kg</t>
-  </si>
-  <si>
-    <t>1. Add 6kg of sugar into a clean preparation container.</t>
-  </si>
-  <si>
-    <t>Hot Water</t>
-  </si>
-  <si>
-    <t>3400ml</t>
-  </si>
-  <si>
-    <t>2. Boil 3400ml of water.</t>
-  </si>
-  <si>
-    <t>3. Pour the hot water into the sugar carefully.</t>
-  </si>
-  <si>
-    <t>4. Mix thoroughly until all sugar is fully dissolved.</t>
-  </si>
-  <si>
-    <t>London Shot</t>
-  </si>
-  <si>
-    <t>10 Days</t>
-  </si>
-  <si>
-    <t>Fridge</t>
-  </si>
-  <si>
-    <t>3400g</t>
-  </si>
-  <si>
-    <t>1. Add Mojito Syrup into a clean preparation container.</t>
-  </si>
-  <si>
-    <t>Whole Shot</t>
-  </si>
-  <si>
-    <t>1P (1905g)</t>
-  </si>
-  <si>
-    <t>2. Add 1 pack of Whole Shot.</t>
-  </si>
-  <si>
-    <t>3. Mix evenly until fully combined.</t>
-  </si>
-  <si>
-    <t>Prep Shot</t>
-  </si>
-  <si>
-    <t>5200g</t>
-  </si>
-  <si>
-    <t>1. Pour London Shot into a clean container.</t>
-  </si>
-  <si>
-    <t>Fresh Lemon</t>
-  </si>
-  <si>
-    <t>250g</t>
-  </si>
-  <si>
-    <t>2. Add freshly squeezed lemon juice.</t>
-  </si>
-  <si>
-    <t>3. Mix thoroughly until evenly combined.</t>
-  </si>
-  <si>
-    <t>4. Store refrigerated.</t>
-  </si>
-  <si>
-    <t>Ultra Shot</t>
-  </si>
-  <si>
-    <t>1200g</t>
-  </si>
-  <si>
-    <t>1. Add Prep Shot into a clean container.</t>
-  </si>
-  <si>
-    <t>Citric Acid</t>
-  </si>
-  <si>
-    <t>100g</t>
-  </si>
-  <si>
-    <t>2. Add citric acid.</t>
-  </si>
-  <si>
-    <t>3. Mix thoroughly until fully dissolved.</t>
-  </si>
-  <si>
-    <t>Original Lemonade</t>
-  </si>
-  <si>
-    <t>72 Hours</t>
-  </si>
-  <si>
-    <t>1. Add Prep Shot into a preparation container.</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>2400g</t>
-  </si>
-  <si>
-    <t>2. Add water.</t>
-  </si>
-  <si>
-    <t>3. Close the lid and shake well until fully combined.</t>
-  </si>
-  <si>
-    <t>Iced Tea</t>
-  </si>
-  <si>
-    <t>12 Hours</t>
-  </si>
-  <si>
-    <t>Tea Packs</t>
-  </si>
-  <si>
-    <t>4 pcs</t>
-  </si>
-  <si>
-    <t>1. Add tea packs into hot water.</t>
-  </si>
-  <si>
-    <t>1500ml</t>
-  </si>
-  <si>
-    <t>2. Brew for 3 minutes.</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>500g</t>
-  </si>
-  <si>
-    <t>3. Remove all tea packs.</t>
-  </si>
-  <si>
-    <t>4. Add ice immediately and stir well.</t>
-  </si>
-  <si>
-    <t>Fresh Fruit</t>
-  </si>
-  <si>
-    <t>Kiwi</t>
-  </si>
-  <si>
-    <t>1/6 slice</t>
-  </si>
-  <si>
-    <t>1. Wash all fruits thoroughly before preparation.</t>
-  </si>
-  <si>
-    <t>Strawberry</t>
-  </si>
-  <si>
-    <t>Quarter cut</t>
-  </si>
-  <si>
-    <t>2. Cut the fruits accourding the size</t>
-  </si>
-  <si>
-    <t>Blueberry</t>
-  </si>
-  <si>
-    <t>No cutting required</t>
-  </si>
-  <si>
-    <t>Always wear gloves when handling fresh fruits.</t>
-  </si>
-  <si>
-    <t>Strawberry source</t>
-  </si>
-  <si>
-    <t>Frozen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen strawberry </t>
-  </si>
-  <si>
-    <t>1000g*5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Defrost strawberries </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar </t>
-  </si>
-  <si>
-    <t>1750g</t>
-  </si>
-  <si>
-    <t>2. Put 1kg of strawberries in a blender</t>
-  </si>
-  <si>
-    <t>3. Put strawberries and sugar into a pot</t>
-  </si>
-  <si>
-    <t>4. Heat to 2000°, stirring continuously for 20 min</t>
-  </si>
-  <si>
-    <t>5. Place the sauce in an ice bath and stir for 10 min</t>
-  </si>
-  <si>
-    <t>6. Pack them</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>Classic</t>
-  </si>
-  <si>
-    <t>Medium (16oz)</t>
-  </si>
-  <si>
-    <t>150g</t>
-  </si>
-  <si>
-    <t>1. Add 150g of ice into a Medium (16oz) cup.</t>
-  </si>
-  <si>
-    <t>300g</t>
-  </si>
-  <si>
-    <t>2. Pour 300g of prepared Original Lemonade</t>
-  </si>
-  <si>
-    <t>Large (24oz)</t>
-  </si>
-  <si>
-    <t>180g</t>
-  </si>
-  <si>
-    <t>1. Add 180g of ice into a Large (24oz) cup.</t>
-  </si>
-  <si>
-    <t>400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Pour 400g of prepared Original Lemonade </t>
-  </si>
-  <si>
-    <t>Fizzy Lemonade</t>
-  </si>
-  <si>
-    <t>82g</t>
-  </si>
-  <si>
-    <t>2. Add 82g of Prep Shot.</t>
-  </si>
-  <si>
-    <t>Sparkling Water</t>
-  </si>
-  <si>
-    <t>240g</t>
-  </si>
-  <si>
-    <t>3. Pour sparkling water and stir well.</t>
-  </si>
-  <si>
-    <t>104g</t>
-  </si>
-  <si>
-    <t>2. Add 104g of Prep Shot.</t>
-  </si>
-  <si>
-    <t>Ultra Lemonade</t>
-  </si>
-  <si>
-    <t>2. Add 82g of Ultra Shot.</t>
-  </si>
-  <si>
-    <t>2. Add 104g of Ultra Shot.</t>
-  </si>
-  <si>
-    <t>Hot</t>
-  </si>
-  <si>
-    <t>Hot Lemonade</t>
-  </si>
-  <si>
-    <t>65g</t>
-  </si>
-  <si>
-    <t>1. Add 65g of Prep Shot into a Medium cup.</t>
-  </si>
-  <si>
-    <t>2. Pour hot water and stir well.</t>
-  </si>
-  <si>
-    <t>Flavor</t>
-  </si>
-  <si>
-    <t>Triple Lemonade</t>
-  </si>
-  <si>
-    <t>2. Add 65g of Prep Shot.</t>
-  </si>
-  <si>
-    <t>50g</t>
-  </si>
-  <si>
-    <t>3. Add fresh lemon juice.</t>
-  </si>
-  <si>
-    <t>4. Pour sparkling water and stir well.</t>
-  </si>
-  <si>
-    <t>Cola Lemonade</t>
-  </si>
-  <si>
-    <t>Cola</t>
-  </si>
-  <si>
-    <t>3. Pour cola and stir well.</t>
-  </si>
-  <si>
-    <t>Fruits&amp;Fizzy (L)</t>
-  </si>
-  <si>
-    <t>Fruits</t>
-  </si>
-  <si>
-    <t>35g</t>
-  </si>
-  <si>
-    <t>1. Add fruits into a Large (24oz) cup and smash fruits</t>
-  </si>
-  <si>
-    <t>2. Add 180g of ice into a Medium (16oz) cup.</t>
-  </si>
-  <si>
-    <t>Prep shot</t>
-  </si>
-  <si>
-    <t>3. Add 104g of Prep Shot.</t>
-  </si>
-  <si>
-    <t>Sparkling</t>
-  </si>
-  <si>
-    <t>Fruits&amp;Tea (L)</t>
-  </si>
-  <si>
-    <t>4. Pour tea and stir well.</t>
-  </si>
-  <si>
-    <t>Strawberry Frozen Lemonade</t>
-  </si>
-  <si>
-    <t>200g</t>
-  </si>
-  <si>
-    <t>1. Add 200g of ice and 30g of water into a blender cup.</t>
+    <t>160g</t>
+  </si>
+  <si>
+    <t>3. Gradually add the powder mixture into the liquid mixture in 3 parts, mixing well until smooth with no lumps remaining.</t>
+  </si>
+  <si>
+    <t>4. Add sunflower oil and mix thoroughly.</t>
+  </si>
+  <si>
+    <t>Whole milk</t>
+  </si>
+  <si>
+    <t>900g</t>
+  </si>
+  <si>
+    <t>Egg</t>
+  </si>
+  <si>
+    <t>4P</t>
+  </si>
+  <si>
+    <t>Sunflower oil</t>
+  </si>
+  <si>
+    <t>20g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crepe whipping cream </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double cream </t>
+  </si>
+  <si>
+    <t>1500g</t>
+  </si>
+  <si>
+    <t>Single cream</t>
+  </si>
+  <si>
+    <t>Matcha Honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mix all matcha and honey </t>
+  </si>
+  <si>
+    <t>Honey</t>
   </si>
   <si>
     <t>30g</t>
   </si>
   <si>
-    <t>3. Add 35g of grapefruit juice.</t>
-  </si>
-  <si>
-    <t>Grapefruit Juice</t>
-  </si>
-  <si>
-    <t>4. Add 65g of strawberry.</t>
-  </si>
-  <si>
-    <t>5. Blend for approximately 20 seconds until smooth.</t>
-  </si>
-  <si>
-    <t>Blueberry Frozen Lemonade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Add 65g of blueberries </t>
-  </si>
-  <si>
-    <t>Kiwi Frozen Lemonade</t>
-  </si>
-  <si>
-    <t>4. Add 65g of kiwi</t>
-  </si>
-  <si>
-    <t>Matcha</t>
-  </si>
-  <si>
-    <t>Matcha Lemonade</t>
-  </si>
-  <si>
-    <t>87g</t>
-  </si>
-  <si>
-    <t>2. Add 87g of Prep Shot.</t>
-  </si>
-  <si>
-    <t>3. Add 240g of water and stir well</t>
-  </si>
-  <si>
-    <t>Matcha Powder</t>
-  </si>
-  <si>
-    <t>2g</t>
-  </si>
-  <si>
-    <t>4. Add 2g of matcha powder and 50g of hot water into matcha bowl</t>
-  </si>
-  <si>
-    <t>Hot water</t>
-  </si>
-  <si>
-    <t>5. Whisk the matcha thoroughly until smooth and formy</t>
-  </si>
-  <si>
-    <t>6. Pour the prepared matcha onto the ice lemonade base</t>
+    <t>Crepe</t>
+  </si>
+  <si>
+    <t>Classic  Matcha crepe</t>
+  </si>
+  <si>
+    <t>Mixture</t>
   </si>
   <si>
     <t>130g</t>
   </si>
   <si>
-    <t>3g</t>
-  </si>
-  <si>
-    <t>4. Add matcha powder and hot water into matcha bowl</t>
-  </si>
-  <si>
-    <t>Strawberry Matcha Lemonade</t>
-  </si>
-  <si>
-    <t>Strawberry Sauce</t>
-  </si>
-  <si>
-    <t>40g</t>
-  </si>
-  <si>
-    <t>1. Add strawberry sauce into a Medium (16oz) cup.</t>
-  </si>
-  <si>
-    <t>2. Add 150g of ice</t>
-  </si>
-  <si>
-    <t>Original Lemonade Base</t>
-  </si>
-  <si>
-    <t>230g</t>
-  </si>
-  <si>
-    <t>3. Add 230g of Original Lemonade Base.</t>
-  </si>
-  <si>
-    <t>Mango Matcha Lemonade</t>
-  </si>
-  <si>
-    <t>Mango Puree</t>
-  </si>
-  <si>
-    <t>1. Add 2 pomp of mango purée into a Medium (16oz) cup.</t>
-  </si>
-  <si>
-    <t>Topping</t>
-  </si>
-  <si>
-    <t>Extra lemon</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.5 P</t>
-  </si>
-  <si>
-    <t>1. Squeeze fresh lemons using the lemon squeezer.</t>
-  </si>
-  <si>
-    <t>2. Add 35ml of fresh lemon juice.</t>
-  </si>
-  <si>
-    <t>Smash Fruits</t>
-  </si>
-  <si>
-    <t>Fresh fruits</t>
-  </si>
-  <si>
-    <t>1. Pour the fruits and smash</t>
+    <t>1. Pour the mixture onto the hot plate and spread evenly.</t>
+  </si>
+  <si>
+    <t>Whipping cream</t>
+  </si>
+  <si>
+    <t>90g</t>
+  </si>
+  <si>
+    <t>2. Cook for approximately 1–2 minutes until lightly coloured.</t>
+  </si>
+  <si>
+    <t>Matcha honey</t>
+  </si>
+  <si>
+    <t>3. Flip the crepe and cook the other side.</t>
+  </si>
+  <si>
+    <t>4. Allow the crepe to cool slightly before adding whipped cream.</t>
+  </si>
+  <si>
+    <t>5g</t>
+  </si>
+  <si>
+    <t>5. Add matcha honey.</t>
+  </si>
+  <si>
+    <t>6. Fold into a triangle shape and place into the package.</t>
+  </si>
+  <si>
+    <t>7. Top with additional whipped cream.</t>
+  </si>
+  <si>
+    <t>8. Add matcha honey on top of the whipped cream.</t>
+  </si>
+  <si>
+    <t>Strawberry Matcha crepe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strawberry source </t>
+  </si>
+  <si>
+    <t>3. Flip the crepe and cook the other side, then allow the crepe to cool slightly.</t>
+  </si>
+  <si>
+    <t>4. Spread strawberry sauce onto the crepe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Strawberry </t>
+  </si>
+  <si>
+    <t>5. Add whipped cream.</t>
+  </si>
+  <si>
+    <t>7. Top with additional whipped cream and matcha honey.</t>
+  </si>
+  <si>
+    <t>8. Slice 1.5 strawberries.</t>
+  </si>
+  <si>
+    <t>9. Place the sliced strawberries on top.</t>
   </si>
 </sst>
 </file>
@@ -551,7 +804,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -591,6 +844,17 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="13.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -612,7 +876,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="36">
     <border/>
     <border>
       <left style="medium">
@@ -917,11 +1181,57 @@
         <color rgb="FF000000"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="125">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1113,6 +1423,132 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="24" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="33" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="34" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1123,6 +1559,123 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1590675" cy="1628775"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="1581150"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1085850" cy="1485900"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1028700" cy="1323975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2285,7 +2838,7 @@
         <v>109</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G57" s="42"/>
     </row>
@@ -2294,29 +2847,29 @@
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E58" s="30" t="s">
         <v>100</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G58" s="41"/>
     </row>
     <row r="59">
       <c r="A59" s="16"/>
       <c r="B59" s="43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>91</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F59" s="14" t="s">
         <v>124</v>
@@ -2345,9 +2898,8 @@
       <c r="D61" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="E61" s="45">
-        <f>82+22</f>
-        <v>104</v>
+      <c r="E61" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="F61" s="20" t="s">
         <v>127</v>
@@ -2378,10 +2930,10 @@
         <v>91</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F63" s="14" t="s">
         <v>124</v>
@@ -2410,9 +2962,8 @@
       <c r="D65" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="E65" s="45">
-        <f>82+22</f>
-        <v>104</v>
+      <c r="E65" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="F65" s="20" t="s">
         <v>127</v>
@@ -2487,615 +3038,597 @@
     </row>
     <row r="70">
       <c r="A70" s="16"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="19" t="s">
+      <c r="B70" s="24"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="31" t="s">
         <v>137</v>
       </c>
       <c r="G70" s="42"/>
     </row>
     <row r="71">
       <c r="A71" s="16"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E71" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F71" s="31" t="s">
+      <c r="B71" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="G71" s="41"/>
+      <c r="C71" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G71" s="40"/>
     </row>
     <row r="72">
       <c r="A72" s="16"/>
-      <c r="B72" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G72" s="40"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="42"/>
     </row>
     <row r="73">
       <c r="A73" s="16"/>
       <c r="B73" s="17"/>
       <c r="C73" s="18"/>
       <c r="D73" s="19" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="G73" s="42"/>
     </row>
     <row r="74">
       <c r="A74" s="16"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>135</v>
+      <c r="B74" s="24"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>137</v>
       </c>
       <c r="G74" s="42"/>
     </row>
     <row r="75">
       <c r="A75" s="16"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F75" s="20" t="s">
+      <c r="B75" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="42"/>
+      <c r="C75" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G75" s="40"/>
     </row>
     <row r="76">
       <c r="A76" s="16"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="E76" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F76" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G76" s="41"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G76" s="42"/>
     </row>
     <row r="77">
       <c r="A77" s="16"/>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="F77" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="G77" s="49"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="34"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="G78" s="41"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D79" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E77" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G77" s="40"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="16"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="G78" s="42"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G79" s="42"/>
+      <c r="E79" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G79" s="40"/>
     </row>
     <row r="80">
       <c r="A80" s="16"/>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
       <c r="D80" s="19" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F80" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G80" s="49"/>
+        <v>145</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G80" s="42"/>
     </row>
     <row r="81">
-      <c r="A81" s="34"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E81" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G81" s="41"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="G81" s="42"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F82" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G82" s="40"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G82" s="42"/>
     </row>
     <row r="83">
       <c r="A83" s="16"/>
       <c r="B83" s="17"/>
       <c r="C83" s="18"/>
       <c r="D83" s="19" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G83" s="42"/>
     </row>
     <row r="84">
       <c r="A84" s="16"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="G84" s="42"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G84" s="41"/>
     </row>
     <row r="85">
       <c r="A85" s="16"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="F85" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G85" s="42"/>
+      <c r="B85" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G85" s="40"/>
     </row>
     <row r="86">
       <c r="A86" s="16"/>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
       <c r="D86" s="19" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G86" s="42"/>
     </row>
     <row r="87">
       <c r="A87" s="16"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="G87" s="41"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="G87" s="42"/>
     </row>
     <row r="88">
       <c r="A88" s="16"/>
-      <c r="B88" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G88" s="40"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="G88" s="42"/>
     </row>
     <row r="89">
       <c r="A89" s="16"/>
       <c r="B89" s="17"/>
       <c r="C89" s="18"/>
       <c r="D89" s="19" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G89" s="42"/>
     </row>
     <row r="90">
       <c r="A90" s="16"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F90" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="G90" s="42"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G90" s="41"/>
     </row>
     <row r="91">
       <c r="A91" s="16"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="F91" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G91" s="42"/>
+      <c r="B91" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F91" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G91" s="40"/>
     </row>
     <row r="92">
       <c r="A92" s="16"/>
       <c r="B92" s="17"/>
       <c r="C92" s="18"/>
       <c r="D92" s="19" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="F92" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="G92" s="42"/>
+        <v>87</v>
+      </c>
+      <c r="F92" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="G92" s="49"/>
     </row>
     <row r="93">
       <c r="A93" s="16"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="G93" s="41"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G93" s="42"/>
     </row>
     <row r="94">
       <c r="A94" s="16"/>
-      <c r="B94" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G94" s="40"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="G94" s="42"/>
     </row>
     <row r="95">
       <c r="A95" s="16"/>
       <c r="B95" s="17"/>
       <c r="C95" s="18"/>
       <c r="D95" s="19" t="s">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F95" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G95" s="49"/>
+        <v>115</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G95" s="42"/>
     </row>
     <row r="96">
       <c r="A96" s="16"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F96" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G96" s="42"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G96" s="41"/>
     </row>
     <row r="97">
       <c r="A97" s="16"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="E97" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="F97" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G97" s="42"/>
+      <c r="B97" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F97" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G97" s="40"/>
     </row>
     <row r="98">
       <c r="A98" s="16"/>
       <c r="B98" s="17"/>
       <c r="C98" s="18"/>
       <c r="D98" s="19" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="F98" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="G98" s="42"/>
+        <v>87</v>
+      </c>
+      <c r="F98" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="G98" s="49"/>
     </row>
     <row r="99">
       <c r="A99" s="16"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="G99" s="41"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G99" s="42"/>
     </row>
     <row r="100">
       <c r="A100" s="16"/>
-      <c r="B100" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G100" s="40"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="G100" s="42"/>
     </row>
     <row r="101">
       <c r="A101" s="16"/>
       <c r="B101" s="17"/>
       <c r="C101" s="18"/>
       <c r="D101" s="19" t="s">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F101" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G101" s="49"/>
+        <v>115</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G101" s="42"/>
     </row>
     <row r="102">
-      <c r="A102" s="16"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E102" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F102" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G102" s="42"/>
+      <c r="A102" s="34"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="G102" s="52"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="54"/>
     </row>
     <row r="103">
-      <c r="A103" s="16"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="F103" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G103" s="42"/>
+      <c r="A103" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="B103" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C103" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D103" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="F103" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="G103" s="60"/>
     </row>
     <row r="104">
       <c r="A104" s="16"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E104" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="F104" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="G104" s="42"/>
+      <c r="B104" s="34"/>
+      <c r="C104" s="61"/>
+      <c r="D104" s="34"/>
+      <c r="E104" s="62"/>
+      <c r="F104" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="G104" s="64"/>
     </row>
     <row r="105">
       <c r="A105" s="34"/>
-      <c r="B105" s="24"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="50"/>
-      <c r="E105" s="50"/>
-      <c r="F105" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="G105" s="52"/>
-      <c r="J105" s="53"/>
-      <c r="K105" s="54"/>
+      <c r="B105" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="C105" s="66" t="s">
+        <v>168</v>
+      </c>
+      <c r="D105" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="E105" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F105" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="G105" s="60"/>
     </row>
     <row r="106">
-      <c r="A106" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="B106" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C106" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D106" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="E106" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="F106" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="G106" s="60"/>
+      <c r="A106" s="69"/>
+      <c r="B106" s="70"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="71"/>
+      <c r="J106" s="72"/>
+      <c r="K106" s="73"/>
     </row>
     <row r="107">
-      <c r="A107" s="16"/>
-      <c r="B107" s="34"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="34"/>
-      <c r="E107" s="62"/>
-      <c r="F107" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="G107" s="64"/>
+      <c r="A107" s="74"/>
+      <c r="B107" s="75"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="71"/>
+      <c r="J107" s="72"/>
+      <c r="K107" s="73"/>
     </row>
     <row r="108">
-      <c r="A108" s="34"/>
-      <c r="B108" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="C108" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="D108" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="E108" s="68" t="s">
-        <v>159</v>
-      </c>
-      <c r="F108" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="G108" s="60"/>
+      <c r="A108" s="74"/>
+      <c r="B108" s="75"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="71"/>
+      <c r="J108" s="72"/>
+      <c r="K108" s="73"/>
     </row>
     <row r="109">
-      <c r="A109" s="69"/>
-      <c r="B109" s="70"/>
+      <c r="A109" s="74"/>
+      <c r="B109" s="75"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="71"/>
-      <c r="J109" s="72"/>
-      <c r="K109" s="73"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="54"/>
     </row>
     <row r="110">
       <c r="A110" s="74"/>
@@ -3116,17 +3649,17 @@
       <c r="K111" s="73"/>
     </row>
     <row r="112">
-      <c r="A112" s="74"/>
-      <c r="B112" s="75"/>
+      <c r="A112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
       <c r="E112" s="71"/>
-      <c r="J112" s="53"/>
-      <c r="K112" s="54"/>
+      <c r="J112" s="72"/>
+      <c r="K112" s="73"/>
     </row>
     <row r="113">
-      <c r="A113" s="74"/>
-      <c r="B113" s="75"/>
+      <c r="A113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="71"/>
@@ -3134,8 +3667,8 @@
       <c r="K113" s="73"/>
     </row>
     <row r="114">
-      <c r="A114" s="74"/>
-      <c r="B114" s="75"/>
+      <c r="A114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="71"/>
@@ -3157,8 +3690,6 @@
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c r="E116" s="71"/>
-      <c r="J116" s="72"/>
-      <c r="K116" s="73"/>
     </row>
     <row r="117">
       <c r="A117" s="69"/>
@@ -3166,8 +3697,6 @@
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="71"/>
-      <c r="J117" s="72"/>
-      <c r="K117" s="73"/>
     </row>
     <row r="118">
       <c r="A118" s="69"/>
@@ -3175,8 +3704,6 @@
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="71"/>
-      <c r="J118" s="72"/>
-      <c r="K118" s="73"/>
     </row>
     <row r="119">
       <c r="A119" s="69"/>
@@ -3403,21 +3930,21 @@
       <c r="E150" s="71"/>
     </row>
     <row r="151">
-      <c r="A151" s="69"/>
+      <c r="A151" s="76"/>
       <c r="B151" s="70"/>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="71"/>
     </row>
     <row r="152">
-      <c r="A152" s="69"/>
+      <c r="A152" s="76"/>
       <c r="B152" s="70"/>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="71"/>
     </row>
     <row r="153">
-      <c r="A153" s="69"/>
+      <c r="A153" s="76"/>
       <c r="B153" s="70"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
@@ -9337,27 +9864,6 @@
       <c r="C998" s="8"/>
       <c r="D998" s="8"/>
       <c r="E998" s="71"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="76"/>
-      <c r="B999" s="70"/>
-      <c r="C999" s="8"/>
-      <c r="D999" s="8"/>
-      <c r="E999" s="71"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="76"/>
-      <c r="B1000" s="70"/>
-      <c r="C1000" s="8"/>
-      <c r="D1000" s="8"/>
-      <c r="E1000" s="71"/>
-    </row>
-    <row r="1001">
-      <c r="A1001" s="76"/>
-      <c r="B1001" s="70"/>
-      <c r="C1001" s="8"/>
-      <c r="D1001" s="8"/>
-      <c r="E1001" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="75">
@@ -9390,10 +9896,10 @@
     <mergeCell ref="C38:C40"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B62"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="D103:D104"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="C50:C51"/>
@@ -9415,27 +9921,4622 @@
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="A52:A66"/>
-    <mergeCell ref="A67:A81"/>
-    <mergeCell ref="A82:A105"/>
-    <mergeCell ref="A106:A108"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="C82:C87"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="C94:C99"/>
-    <mergeCell ref="C100:C105"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="B94:B99"/>
-    <mergeCell ref="B100:B105"/>
-    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A67:A78"/>
+    <mergeCell ref="A79:A102"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C79:C84"/>
+    <mergeCell ref="C85:C90"/>
+    <mergeCell ref="C91:C96"/>
+    <mergeCell ref="C97:C102"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B103:B104"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B85:B90"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="31.0"/>
+    <col customWidth="1" min="3" max="3" width="19.0"/>
+    <col customWidth="1" min="4" max="4" width="8.5"/>
+    <col customWidth="1" min="5" max="5" width="88.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="33.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="78"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18"/>
+      <c r="B5" s="82" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="84" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="84" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="85"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18"/>
+      <c r="B8" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="86"/>
+      <c r="D8" s="84" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="85"/>
+      <c r="B9" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="84" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="87" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="20" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18"/>
+      <c r="B21" s="82" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="89" t="s">
+        <v>199</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="92"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="92"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="I25" s="90"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="92"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="I26" s="90"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="92"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="I27" s="90"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="92"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="I28" s="90"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="92"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="I29" s="90"/>
+      <c r="J29" s="91"/>
+      <c r="K29" s="92"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="85"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="I30" s="90"/>
+      <c r="J30" s="91"/>
+      <c r="K30" s="92"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="80" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="90"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="92"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" s="82" t="s">
+        <v>212</v>
+      </c>
+      <c r="C32" s="93" t="s">
+        <v>213</v>
+      </c>
+      <c r="D32" s="94" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I32" s="90"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="92"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="95" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="94" t="s">
+        <v>216</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="I33" s="96"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="92"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="95" t="s">
+        <v>218</v>
+      </c>
+      <c r="D34" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="95" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="82" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="94" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36" s="94" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="94" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="G38" s="97"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="95" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" s="94" t="s">
+        <v>227</v>
+      </c>
+      <c r="E39" s="85"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18"/>
+      <c r="B40" s="82" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="D40" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="H40" s="99"/>
+      <c r="I40" s="100"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="98" t="s">
+        <v>231</v>
+      </c>
+      <c r="D41" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="82" t="s">
+        <v>187</v>
+      </c>
+      <c r="H41" s="99"/>
+      <c r="I41" s="100"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="E42" s="85"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18"/>
+      <c r="B43" s="82" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="101" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="82" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="85"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="101" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" s="94" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" s="85"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="B45" s="103" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" s="104" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="105" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="106" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="106" t="s">
+        <v>241</v>
+      </c>
+      <c r="D48" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="102" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="108" t="s">
+        <v>247</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="109"/>
+      <c r="D50" s="110"/>
+      <c r="E50" s="20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="111"/>
+      <c r="D51" s="112"/>
+      <c r="E51" s="20" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="113"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18"/>
+      <c r="B53" s="115" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" s="95" t="s">
+        <v>238</v>
+      </c>
+      <c r="D53" s="95">
+        <v>130.0</v>
+      </c>
+      <c r="E53" s="116" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18"/>
+      <c r="B54" s="111"/>
+      <c r="C54" s="108" t="s">
+        <v>253</v>
+      </c>
+      <c r="D54" s="117">
+        <v>15.0</v>
+      </c>
+      <c r="E54" s="116" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18"/>
+      <c r="B55" s="111"/>
+      <c r="C55" s="95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D55" s="95">
+        <v>90.0</v>
+      </c>
+      <c r="E55" s="116" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18"/>
+      <c r="B56" s="111"/>
+      <c r="C56" s="95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="95">
+        <v>30.0</v>
+      </c>
+      <c r="E56" s="116" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18"/>
+      <c r="B57" s="111"/>
+      <c r="C57" s="117" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" s="117">
+        <v>20.0</v>
+      </c>
+      <c r="E57" s="116" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18"/>
+      <c r="B58" s="111"/>
+      <c r="C58" s="118" t="s">
+        <v>232</v>
+      </c>
+      <c r="D58" s="108" t="s">
+        <v>247</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18"/>
+      <c r="B59" s="111"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="110"/>
+      <c r="E59" s="20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18"/>
+      <c r="B60" s="111"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="85"/>
+      <c r="B61" s="113"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="114"/>
+      <c r="E61" s="20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="120"/>
+      <c r="C62" s="121"/>
+      <c r="D62" s="121"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="96"/>
+      <c r="C63" s="121"/>
+      <c r="D63" s="121"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="96"/>
+      <c r="C64" s="121"/>
+      <c r="D64" s="121"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="96"/>
+      <c r="C65" s="121"/>
+      <c r="D65" s="121"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="121"/>
+      <c r="D66" s="121"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="121"/>
+      <c r="D67" s="121"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="121"/>
+      <c r="D68" s="121"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="121"/>
+      <c r="D69" s="121"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="121"/>
+      <c r="D70" s="121"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="121"/>
+      <c r="D71" s="122"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="121"/>
+      <c r="D72" s="121"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="121"/>
+      <c r="D73" s="121"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="122"/>
+      <c r="D74" s="122"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="121"/>
+      <c r="D75" s="121"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="121"/>
+      <c r="D76" s="121"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="122"/>
+      <c r="D77" s="122"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="121"/>
+      <c r="D78" s="121"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="123"/>
+      <c r="D79" s="124"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="123"/>
+      <c r="D80" s="124"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="123"/>
+      <c r="D81" s="124"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="123"/>
+      <c r="D82" s="124"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="123"/>
+      <c r="D83" s="124"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="123"/>
+      <c r="D84" s="124"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="123"/>
+      <c r="D85" s="124"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="123"/>
+      <c r="D86" s="124"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="123"/>
+      <c r="D87" s="124"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="123"/>
+      <c r="D88" s="124"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="123"/>
+      <c r="D89" s="124"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="123"/>
+      <c r="D90" s="124"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="123"/>
+      <c r="D91" s="124"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="123"/>
+      <c r="D92" s="124"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="123"/>
+      <c r="D93" s="124"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="123"/>
+      <c r="D94" s="124"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="123"/>
+      <c r="D95" s="124"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="123"/>
+      <c r="D96" s="124"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="123"/>
+      <c r="D97" s="124"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="123"/>
+      <c r="D98" s="124"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="123"/>
+      <c r="D99" s="124"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="123"/>
+      <c r="D100" s="124"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="123"/>
+      <c r="D101" s="124"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="123"/>
+      <c r="D102" s="124"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="123"/>
+      <c r="D103" s="124"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="123"/>
+      <c r="D104" s="124"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="123"/>
+      <c r="D105" s="124"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="123"/>
+      <c r="D106" s="124"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="123"/>
+      <c r="D107" s="124"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="123"/>
+      <c r="D108" s="124"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="123"/>
+      <c r="D109" s="124"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="123"/>
+      <c r="D110" s="124"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="123"/>
+      <c r="D111" s="124"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="123"/>
+      <c r="D112" s="124"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="123"/>
+      <c r="D113" s="124"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="123"/>
+      <c r="D114" s="124"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="123"/>
+      <c r="D115" s="124"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="123"/>
+      <c r="D116" s="124"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="123"/>
+      <c r="D117" s="124"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="123"/>
+      <c r="D118" s="124"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="123"/>
+      <c r="D119" s="124"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="123"/>
+      <c r="D120" s="124"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="123"/>
+      <c r="D121" s="124"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="123"/>
+      <c r="D122" s="124"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="123"/>
+      <c r="D123" s="124"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="123"/>
+      <c r="D124" s="124"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="123"/>
+      <c r="D125" s="124"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="123"/>
+      <c r="D126" s="124"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="123"/>
+      <c r="D127" s="124"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="123"/>
+      <c r="D128" s="124"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="123"/>
+      <c r="D129" s="124"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="123"/>
+      <c r="D130" s="124"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="123"/>
+      <c r="D131" s="124"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="123"/>
+      <c r="D132" s="124"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="123"/>
+      <c r="D133" s="124"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="123"/>
+      <c r="D134" s="124"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="123"/>
+      <c r="D135" s="124"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="123"/>
+      <c r="D136" s="124"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="123"/>
+      <c r="D137" s="124"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="123"/>
+      <c r="D138" s="124"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="123"/>
+      <c r="D139" s="124"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="123"/>
+      <c r="D140" s="124"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="123"/>
+      <c r="D141" s="124"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="123"/>
+      <c r="D142" s="124"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="123"/>
+      <c r="D143" s="124"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="123"/>
+      <c r="D144" s="124"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="123"/>
+      <c r="D145" s="124"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="123"/>
+      <c r="D146" s="124"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="123"/>
+      <c r="D147" s="124"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="123"/>
+      <c r="D148" s="124"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="123"/>
+      <c r="D149" s="124"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="123"/>
+      <c r="D150" s="124"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="123"/>
+      <c r="D151" s="124"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="123"/>
+      <c r="D152" s="124"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="123"/>
+      <c r="D153" s="124"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="123"/>
+      <c r="D154" s="124"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="123"/>
+      <c r="D155" s="124"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="123"/>
+      <c r="D156" s="124"/>
+    </row>
+    <row r="157">
+      <c r="C157" s="123"/>
+      <c r="D157" s="124"/>
+    </row>
+    <row r="158">
+      <c r="C158" s="123"/>
+      <c r="D158" s="124"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="123"/>
+      <c r="D159" s="124"/>
+    </row>
+    <row r="160">
+      <c r="C160" s="123"/>
+      <c r="D160" s="124"/>
+    </row>
+    <row r="161">
+      <c r="C161" s="123"/>
+      <c r="D161" s="124"/>
+    </row>
+    <row r="162">
+      <c r="C162" s="123"/>
+      <c r="D162" s="124"/>
+    </row>
+    <row r="163">
+      <c r="C163" s="123"/>
+      <c r="D163" s="124"/>
+    </row>
+    <row r="164">
+      <c r="C164" s="123"/>
+      <c r="D164" s="124"/>
+    </row>
+    <row r="165">
+      <c r="C165" s="123"/>
+      <c r="D165" s="124"/>
+    </row>
+    <row r="166">
+      <c r="C166" s="123"/>
+      <c r="D166" s="124"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="123"/>
+      <c r="D167" s="124"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="123"/>
+      <c r="D168" s="124"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="123"/>
+      <c r="D169" s="124"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="123"/>
+      <c r="D170" s="124"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="123"/>
+      <c r="D171" s="124"/>
+    </row>
+    <row r="172">
+      <c r="C172" s="123"/>
+      <c r="D172" s="124"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="123"/>
+      <c r="D173" s="124"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="123"/>
+      <c r="D174" s="124"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="123"/>
+      <c r="D175" s="124"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="123"/>
+      <c r="D176" s="124"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="123"/>
+      <c r="D177" s="124"/>
+    </row>
+    <row r="178">
+      <c r="C178" s="123"/>
+      <c r="D178" s="124"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="123"/>
+      <c r="D179" s="124"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="123"/>
+      <c r="D180" s="124"/>
+    </row>
+    <row r="181">
+      <c r="C181" s="123"/>
+      <c r="D181" s="124"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="123"/>
+      <c r="D182" s="124"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="123"/>
+      <c r="D183" s="124"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="123"/>
+      <c r="D184" s="124"/>
+    </row>
+    <row r="185">
+      <c r="C185" s="123"/>
+      <c r="D185" s="124"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="123"/>
+      <c r="D186" s="124"/>
+    </row>
+    <row r="187">
+      <c r="C187" s="123"/>
+      <c r="D187" s="124"/>
+    </row>
+    <row r="188">
+      <c r="C188" s="123"/>
+      <c r="D188" s="124"/>
+    </row>
+    <row r="189">
+      <c r="C189" s="123"/>
+      <c r="D189" s="124"/>
+    </row>
+    <row r="190">
+      <c r="C190" s="123"/>
+      <c r="D190" s="124"/>
+    </row>
+    <row r="191">
+      <c r="C191" s="123"/>
+      <c r="D191" s="124"/>
+    </row>
+    <row r="192">
+      <c r="C192" s="123"/>
+      <c r="D192" s="124"/>
+    </row>
+    <row r="193">
+      <c r="C193" s="123"/>
+      <c r="D193" s="124"/>
+    </row>
+    <row r="194">
+      <c r="C194" s="123"/>
+      <c r="D194" s="124"/>
+    </row>
+    <row r="195">
+      <c r="C195" s="123"/>
+      <c r="D195" s="124"/>
+    </row>
+    <row r="196">
+      <c r="C196" s="123"/>
+      <c r="D196" s="124"/>
+    </row>
+    <row r="197">
+      <c r="C197" s="123"/>
+      <c r="D197" s="124"/>
+    </row>
+    <row r="198">
+      <c r="C198" s="123"/>
+      <c r="D198" s="124"/>
+    </row>
+    <row r="199">
+      <c r="C199" s="123"/>
+      <c r="D199" s="124"/>
+    </row>
+    <row r="200">
+      <c r="C200" s="123"/>
+      <c r="D200" s="124"/>
+    </row>
+    <row r="201">
+      <c r="C201" s="123"/>
+      <c r="D201" s="124"/>
+    </row>
+    <row r="202">
+      <c r="C202" s="123"/>
+      <c r="D202" s="124"/>
+    </row>
+    <row r="203">
+      <c r="C203" s="123"/>
+      <c r="D203" s="124"/>
+    </row>
+    <row r="204">
+      <c r="C204" s="123"/>
+      <c r="D204" s="124"/>
+    </row>
+    <row r="205">
+      <c r="C205" s="123"/>
+      <c r="D205" s="124"/>
+    </row>
+    <row r="206">
+      <c r="C206" s="123"/>
+      <c r="D206" s="124"/>
+    </row>
+    <row r="207">
+      <c r="C207" s="123"/>
+      <c r="D207" s="124"/>
+    </row>
+    <row r="208">
+      <c r="C208" s="123"/>
+      <c r="D208" s="124"/>
+    </row>
+    <row r="209">
+      <c r="C209" s="123"/>
+      <c r="D209" s="124"/>
+    </row>
+    <row r="210">
+      <c r="C210" s="123"/>
+      <c r="D210" s="124"/>
+    </row>
+    <row r="211">
+      <c r="C211" s="123"/>
+      <c r="D211" s="124"/>
+    </row>
+    <row r="212">
+      <c r="C212" s="123"/>
+      <c r="D212" s="124"/>
+    </row>
+    <row r="213">
+      <c r="C213" s="123"/>
+      <c r="D213" s="124"/>
+    </row>
+    <row r="214">
+      <c r="C214" s="123"/>
+      <c r="D214" s="124"/>
+    </row>
+    <row r="215">
+      <c r="C215" s="123"/>
+      <c r="D215" s="124"/>
+    </row>
+    <row r="216">
+      <c r="C216" s="123"/>
+      <c r="D216" s="124"/>
+    </row>
+    <row r="217">
+      <c r="C217" s="123"/>
+      <c r="D217" s="124"/>
+    </row>
+    <row r="218">
+      <c r="C218" s="123"/>
+      <c r="D218" s="124"/>
+    </row>
+    <row r="219">
+      <c r="C219" s="123"/>
+      <c r="D219" s="124"/>
+    </row>
+    <row r="220">
+      <c r="C220" s="123"/>
+      <c r="D220" s="124"/>
+    </row>
+    <row r="221">
+      <c r="C221" s="123"/>
+      <c r="D221" s="124"/>
+    </row>
+    <row r="222">
+      <c r="C222" s="123"/>
+      <c r="D222" s="124"/>
+    </row>
+    <row r="223">
+      <c r="C223" s="123"/>
+      <c r="D223" s="124"/>
+    </row>
+    <row r="224">
+      <c r="C224" s="123"/>
+      <c r="D224" s="124"/>
+    </row>
+    <row r="225">
+      <c r="C225" s="123"/>
+      <c r="D225" s="124"/>
+    </row>
+    <row r="226">
+      <c r="C226" s="123"/>
+      <c r="D226" s="124"/>
+    </row>
+    <row r="227">
+      <c r="C227" s="123"/>
+      <c r="D227" s="124"/>
+    </row>
+    <row r="228">
+      <c r="C228" s="123"/>
+      <c r="D228" s="124"/>
+    </row>
+    <row r="229">
+      <c r="C229" s="123"/>
+      <c r="D229" s="124"/>
+    </row>
+    <row r="230">
+      <c r="C230" s="123"/>
+      <c r="D230" s="124"/>
+    </row>
+    <row r="231">
+      <c r="C231" s="123"/>
+      <c r="D231" s="124"/>
+    </row>
+    <row r="232">
+      <c r="C232" s="123"/>
+      <c r="D232" s="124"/>
+    </row>
+    <row r="233">
+      <c r="C233" s="123"/>
+      <c r="D233" s="124"/>
+    </row>
+    <row r="234">
+      <c r="C234" s="123"/>
+      <c r="D234" s="124"/>
+    </row>
+    <row r="235">
+      <c r="C235" s="123"/>
+      <c r="D235" s="124"/>
+    </row>
+    <row r="236">
+      <c r="C236" s="123"/>
+      <c r="D236" s="124"/>
+    </row>
+    <row r="237">
+      <c r="C237" s="123"/>
+      <c r="D237" s="124"/>
+    </row>
+    <row r="238">
+      <c r="C238" s="123"/>
+      <c r="D238" s="124"/>
+    </row>
+    <row r="239">
+      <c r="C239" s="123"/>
+      <c r="D239" s="124"/>
+    </row>
+    <row r="240">
+      <c r="C240" s="123"/>
+      <c r="D240" s="124"/>
+    </row>
+    <row r="241">
+      <c r="C241" s="123"/>
+      <c r="D241" s="124"/>
+    </row>
+    <row r="242">
+      <c r="C242" s="123"/>
+      <c r="D242" s="124"/>
+    </row>
+    <row r="243">
+      <c r="C243" s="123"/>
+      <c r="D243" s="124"/>
+    </row>
+    <row r="244">
+      <c r="C244" s="123"/>
+      <c r="D244" s="124"/>
+    </row>
+    <row r="245">
+      <c r="C245" s="123"/>
+      <c r="D245" s="124"/>
+    </row>
+    <row r="246">
+      <c r="C246" s="123"/>
+      <c r="D246" s="124"/>
+    </row>
+    <row r="247">
+      <c r="C247" s="123"/>
+      <c r="D247" s="124"/>
+    </row>
+    <row r="248">
+      <c r="C248" s="123"/>
+      <c r="D248" s="124"/>
+    </row>
+    <row r="249">
+      <c r="C249" s="123"/>
+      <c r="D249" s="124"/>
+    </row>
+    <row r="250">
+      <c r="C250" s="123"/>
+      <c r="D250" s="124"/>
+    </row>
+    <row r="251">
+      <c r="C251" s="123"/>
+      <c r="D251" s="124"/>
+    </row>
+    <row r="252">
+      <c r="C252" s="123"/>
+      <c r="D252" s="124"/>
+    </row>
+    <row r="253">
+      <c r="C253" s="123"/>
+      <c r="D253" s="124"/>
+    </row>
+    <row r="254">
+      <c r="C254" s="123"/>
+      <c r="D254" s="124"/>
+    </row>
+    <row r="255">
+      <c r="C255" s="123"/>
+      <c r="D255" s="124"/>
+    </row>
+    <row r="256">
+      <c r="C256" s="123"/>
+      <c r="D256" s="124"/>
+    </row>
+    <row r="257">
+      <c r="C257" s="123"/>
+      <c r="D257" s="124"/>
+    </row>
+    <row r="258">
+      <c r="C258" s="123"/>
+      <c r="D258" s="124"/>
+    </row>
+    <row r="259">
+      <c r="C259" s="123"/>
+      <c r="D259" s="124"/>
+    </row>
+    <row r="260">
+      <c r="C260" s="123"/>
+      <c r="D260" s="124"/>
+    </row>
+    <row r="261">
+      <c r="C261" s="123"/>
+      <c r="D261" s="124"/>
+    </row>
+    <row r="262">
+      <c r="C262" s="123"/>
+      <c r="D262" s="124"/>
+    </row>
+    <row r="263">
+      <c r="C263" s="123"/>
+      <c r="D263" s="124"/>
+    </row>
+    <row r="264">
+      <c r="C264" s="123"/>
+      <c r="D264" s="124"/>
+    </row>
+    <row r="265">
+      <c r="C265" s="123"/>
+      <c r="D265" s="124"/>
+    </row>
+    <row r="266">
+      <c r="C266" s="123"/>
+      <c r="D266" s="124"/>
+    </row>
+    <row r="267">
+      <c r="C267" s="123"/>
+      <c r="D267" s="124"/>
+    </row>
+    <row r="268">
+      <c r="C268" s="123"/>
+      <c r="D268" s="124"/>
+    </row>
+    <row r="269">
+      <c r="C269" s="123"/>
+      <c r="D269" s="124"/>
+    </row>
+    <row r="270">
+      <c r="C270" s="123"/>
+      <c r="D270" s="124"/>
+    </row>
+    <row r="271">
+      <c r="C271" s="123"/>
+      <c r="D271" s="124"/>
+    </row>
+    <row r="272">
+      <c r="C272" s="123"/>
+      <c r="D272" s="124"/>
+    </row>
+    <row r="273">
+      <c r="C273" s="123"/>
+      <c r="D273" s="124"/>
+    </row>
+    <row r="274">
+      <c r="C274" s="123"/>
+      <c r="D274" s="124"/>
+    </row>
+    <row r="275">
+      <c r="C275" s="123"/>
+      <c r="D275" s="124"/>
+    </row>
+    <row r="276">
+      <c r="C276" s="123"/>
+      <c r="D276" s="124"/>
+    </row>
+    <row r="277">
+      <c r="C277" s="123"/>
+      <c r="D277" s="124"/>
+    </row>
+    <row r="278">
+      <c r="C278" s="123"/>
+      <c r="D278" s="124"/>
+    </row>
+    <row r="279">
+      <c r="C279" s="123"/>
+      <c r="D279" s="124"/>
+    </row>
+    <row r="280">
+      <c r="C280" s="123"/>
+      <c r="D280" s="124"/>
+    </row>
+    <row r="281">
+      <c r="C281" s="123"/>
+      <c r="D281" s="124"/>
+    </row>
+    <row r="282">
+      <c r="C282" s="123"/>
+      <c r="D282" s="124"/>
+    </row>
+    <row r="283">
+      <c r="C283" s="123"/>
+      <c r="D283" s="124"/>
+    </row>
+    <row r="284">
+      <c r="C284" s="123"/>
+      <c r="D284" s="124"/>
+    </row>
+    <row r="285">
+      <c r="C285" s="123"/>
+      <c r="D285" s="124"/>
+    </row>
+    <row r="286">
+      <c r="C286" s="123"/>
+      <c r="D286" s="124"/>
+    </row>
+    <row r="287">
+      <c r="C287" s="123"/>
+      <c r="D287" s="124"/>
+    </row>
+    <row r="288">
+      <c r="C288" s="123"/>
+      <c r="D288" s="124"/>
+    </row>
+    <row r="289">
+      <c r="C289" s="123"/>
+      <c r="D289" s="124"/>
+    </row>
+    <row r="290">
+      <c r="C290" s="123"/>
+      <c r="D290" s="124"/>
+    </row>
+    <row r="291">
+      <c r="C291" s="123"/>
+      <c r="D291" s="124"/>
+    </row>
+    <row r="292">
+      <c r="C292" s="123"/>
+      <c r="D292" s="124"/>
+    </row>
+    <row r="293">
+      <c r="C293" s="123"/>
+      <c r="D293" s="124"/>
+    </row>
+    <row r="294">
+      <c r="C294" s="123"/>
+      <c r="D294" s="124"/>
+    </row>
+    <row r="295">
+      <c r="C295" s="123"/>
+      <c r="D295" s="124"/>
+    </row>
+    <row r="296">
+      <c r="C296" s="123"/>
+      <c r="D296" s="124"/>
+    </row>
+    <row r="297">
+      <c r="C297" s="123"/>
+      <c r="D297" s="124"/>
+    </row>
+    <row r="298">
+      <c r="C298" s="123"/>
+      <c r="D298" s="124"/>
+    </row>
+    <row r="299">
+      <c r="C299" s="123"/>
+      <c r="D299" s="124"/>
+    </row>
+    <row r="300">
+      <c r="C300" s="123"/>
+      <c r="D300" s="124"/>
+    </row>
+    <row r="301">
+      <c r="C301" s="123"/>
+      <c r="D301" s="124"/>
+    </row>
+    <row r="302">
+      <c r="C302" s="123"/>
+      <c r="D302" s="124"/>
+    </row>
+    <row r="303">
+      <c r="C303" s="123"/>
+      <c r="D303" s="124"/>
+    </row>
+    <row r="304">
+      <c r="C304" s="123"/>
+      <c r="D304" s="124"/>
+    </row>
+    <row r="305">
+      <c r="C305" s="123"/>
+      <c r="D305" s="124"/>
+    </row>
+    <row r="306">
+      <c r="C306" s="123"/>
+      <c r="D306" s="124"/>
+    </row>
+    <row r="307">
+      <c r="C307" s="123"/>
+      <c r="D307" s="124"/>
+    </row>
+    <row r="308">
+      <c r="C308" s="123"/>
+      <c r="D308" s="124"/>
+    </row>
+    <row r="309">
+      <c r="C309" s="123"/>
+      <c r="D309" s="124"/>
+    </row>
+    <row r="310">
+      <c r="C310" s="123"/>
+      <c r="D310" s="124"/>
+    </row>
+    <row r="311">
+      <c r="C311" s="123"/>
+      <c r="D311" s="124"/>
+    </row>
+    <row r="312">
+      <c r="C312" s="123"/>
+      <c r="D312" s="124"/>
+    </row>
+    <row r="313">
+      <c r="C313" s="123"/>
+      <c r="D313" s="124"/>
+    </row>
+    <row r="314">
+      <c r="C314" s="123"/>
+      <c r="D314" s="124"/>
+    </row>
+    <row r="315">
+      <c r="C315" s="123"/>
+      <c r="D315" s="124"/>
+    </row>
+    <row r="316">
+      <c r="C316" s="123"/>
+      <c r="D316" s="124"/>
+    </row>
+    <row r="317">
+      <c r="C317" s="123"/>
+      <c r="D317" s="124"/>
+    </row>
+    <row r="318">
+      <c r="C318" s="123"/>
+      <c r="D318" s="124"/>
+    </row>
+    <row r="319">
+      <c r="C319" s="123"/>
+      <c r="D319" s="124"/>
+    </row>
+    <row r="320">
+      <c r="C320" s="123"/>
+      <c r="D320" s="124"/>
+    </row>
+    <row r="321">
+      <c r="C321" s="123"/>
+      <c r="D321" s="124"/>
+    </row>
+    <row r="322">
+      <c r="C322" s="123"/>
+      <c r="D322" s="124"/>
+    </row>
+    <row r="323">
+      <c r="C323" s="123"/>
+      <c r="D323" s="124"/>
+    </row>
+    <row r="324">
+      <c r="C324" s="123"/>
+      <c r="D324" s="124"/>
+    </row>
+    <row r="325">
+      <c r="C325" s="123"/>
+      <c r="D325" s="124"/>
+    </row>
+    <row r="326">
+      <c r="C326" s="123"/>
+      <c r="D326" s="124"/>
+    </row>
+    <row r="327">
+      <c r="C327" s="123"/>
+      <c r="D327" s="124"/>
+    </row>
+    <row r="328">
+      <c r="C328" s="123"/>
+      <c r="D328" s="124"/>
+    </row>
+    <row r="329">
+      <c r="C329" s="123"/>
+      <c r="D329" s="124"/>
+    </row>
+    <row r="330">
+      <c r="C330" s="123"/>
+      <c r="D330" s="124"/>
+    </row>
+    <row r="331">
+      <c r="C331" s="123"/>
+      <c r="D331" s="124"/>
+    </row>
+    <row r="332">
+      <c r="C332" s="123"/>
+      <c r="D332" s="124"/>
+    </row>
+    <row r="333">
+      <c r="C333" s="123"/>
+      <c r="D333" s="124"/>
+    </row>
+    <row r="334">
+      <c r="C334" s="123"/>
+      <c r="D334" s="124"/>
+    </row>
+    <row r="335">
+      <c r="C335" s="123"/>
+      <c r="D335" s="124"/>
+    </row>
+    <row r="336">
+      <c r="C336" s="123"/>
+      <c r="D336" s="124"/>
+    </row>
+    <row r="337">
+      <c r="C337" s="123"/>
+      <c r="D337" s="124"/>
+    </row>
+    <row r="338">
+      <c r="C338" s="123"/>
+      <c r="D338" s="124"/>
+    </row>
+    <row r="339">
+      <c r="C339" s="123"/>
+      <c r="D339" s="124"/>
+    </row>
+    <row r="340">
+      <c r="C340" s="123"/>
+      <c r="D340" s="124"/>
+    </row>
+    <row r="341">
+      <c r="C341" s="123"/>
+      <c r="D341" s="124"/>
+    </row>
+    <row r="342">
+      <c r="C342" s="123"/>
+      <c r="D342" s="124"/>
+    </row>
+    <row r="343">
+      <c r="C343" s="123"/>
+      <c r="D343" s="124"/>
+    </row>
+    <row r="344">
+      <c r="C344" s="123"/>
+      <c r="D344" s="124"/>
+    </row>
+    <row r="345">
+      <c r="C345" s="123"/>
+      <c r="D345" s="124"/>
+    </row>
+    <row r="346">
+      <c r="C346" s="123"/>
+      <c r="D346" s="124"/>
+    </row>
+    <row r="347">
+      <c r="C347" s="123"/>
+      <c r="D347" s="124"/>
+    </row>
+    <row r="348">
+      <c r="C348" s="123"/>
+      <c r="D348" s="124"/>
+    </row>
+    <row r="349">
+      <c r="C349" s="123"/>
+      <c r="D349" s="124"/>
+    </row>
+    <row r="350">
+      <c r="C350" s="123"/>
+      <c r="D350" s="124"/>
+    </row>
+    <row r="351">
+      <c r="C351" s="123"/>
+      <c r="D351" s="124"/>
+    </row>
+    <row r="352">
+      <c r="C352" s="123"/>
+      <c r="D352" s="124"/>
+    </row>
+    <row r="353">
+      <c r="C353" s="123"/>
+      <c r="D353" s="124"/>
+    </row>
+    <row r="354">
+      <c r="C354" s="123"/>
+      <c r="D354" s="124"/>
+    </row>
+    <row r="355">
+      <c r="C355" s="123"/>
+      <c r="D355" s="124"/>
+    </row>
+    <row r="356">
+      <c r="C356" s="123"/>
+      <c r="D356" s="124"/>
+    </row>
+    <row r="357">
+      <c r="C357" s="123"/>
+      <c r="D357" s="124"/>
+    </row>
+    <row r="358">
+      <c r="C358" s="123"/>
+      <c r="D358" s="124"/>
+    </row>
+    <row r="359">
+      <c r="C359" s="123"/>
+      <c r="D359" s="124"/>
+    </row>
+    <row r="360">
+      <c r="C360" s="123"/>
+      <c r="D360" s="124"/>
+    </row>
+    <row r="361">
+      <c r="C361" s="123"/>
+      <c r="D361" s="124"/>
+    </row>
+    <row r="362">
+      <c r="C362" s="123"/>
+      <c r="D362" s="124"/>
+    </row>
+    <row r="363">
+      <c r="C363" s="123"/>
+      <c r="D363" s="124"/>
+    </row>
+    <row r="364">
+      <c r="C364" s="123"/>
+      <c r="D364" s="124"/>
+    </row>
+    <row r="365">
+      <c r="C365" s="123"/>
+      <c r="D365" s="124"/>
+    </row>
+    <row r="366">
+      <c r="C366" s="123"/>
+      <c r="D366" s="124"/>
+    </row>
+    <row r="367">
+      <c r="C367" s="123"/>
+      <c r="D367" s="124"/>
+    </row>
+    <row r="368">
+      <c r="C368" s="123"/>
+      <c r="D368" s="124"/>
+    </row>
+    <row r="369">
+      <c r="C369" s="123"/>
+      <c r="D369" s="124"/>
+    </row>
+    <row r="370">
+      <c r="C370" s="123"/>
+      <c r="D370" s="124"/>
+    </row>
+    <row r="371">
+      <c r="C371" s="123"/>
+      <c r="D371" s="124"/>
+    </row>
+    <row r="372">
+      <c r="C372" s="123"/>
+      <c r="D372" s="124"/>
+    </row>
+    <row r="373">
+      <c r="C373" s="123"/>
+      <c r="D373" s="124"/>
+    </row>
+    <row r="374">
+      <c r="C374" s="123"/>
+      <c r="D374" s="124"/>
+    </row>
+    <row r="375">
+      <c r="C375" s="123"/>
+      <c r="D375" s="124"/>
+    </row>
+    <row r="376">
+      <c r="C376" s="123"/>
+      <c r="D376" s="124"/>
+    </row>
+    <row r="377">
+      <c r="C377" s="123"/>
+      <c r="D377" s="124"/>
+    </row>
+    <row r="378">
+      <c r="C378" s="123"/>
+      <c r="D378" s="124"/>
+    </row>
+    <row r="379">
+      <c r="C379" s="123"/>
+      <c r="D379" s="124"/>
+    </row>
+    <row r="380">
+      <c r="C380" s="123"/>
+      <c r="D380" s="124"/>
+    </row>
+    <row r="381">
+      <c r="C381" s="123"/>
+      <c r="D381" s="124"/>
+    </row>
+    <row r="382">
+      <c r="C382" s="123"/>
+      <c r="D382" s="124"/>
+    </row>
+    <row r="383">
+      <c r="C383" s="123"/>
+      <c r="D383" s="124"/>
+    </row>
+    <row r="384">
+      <c r="C384" s="123"/>
+      <c r="D384" s="124"/>
+    </row>
+    <row r="385">
+      <c r="C385" s="123"/>
+      <c r="D385" s="124"/>
+    </row>
+    <row r="386">
+      <c r="C386" s="123"/>
+      <c r="D386" s="124"/>
+    </row>
+    <row r="387">
+      <c r="C387" s="123"/>
+      <c r="D387" s="124"/>
+    </row>
+    <row r="388">
+      <c r="C388" s="123"/>
+      <c r="D388" s="124"/>
+    </row>
+    <row r="389">
+      <c r="C389" s="123"/>
+      <c r="D389" s="124"/>
+    </row>
+    <row r="390">
+      <c r="C390" s="123"/>
+      <c r="D390" s="124"/>
+    </row>
+    <row r="391">
+      <c r="C391" s="123"/>
+      <c r="D391" s="124"/>
+    </row>
+    <row r="392">
+      <c r="C392" s="123"/>
+      <c r="D392" s="124"/>
+    </row>
+    <row r="393">
+      <c r="C393" s="123"/>
+      <c r="D393" s="124"/>
+    </row>
+    <row r="394">
+      <c r="C394" s="123"/>
+      <c r="D394" s="124"/>
+    </row>
+    <row r="395">
+      <c r="C395" s="123"/>
+      <c r="D395" s="124"/>
+    </row>
+    <row r="396">
+      <c r="C396" s="123"/>
+      <c r="D396" s="124"/>
+    </row>
+    <row r="397">
+      <c r="C397" s="123"/>
+      <c r="D397" s="124"/>
+    </row>
+    <row r="398">
+      <c r="C398" s="123"/>
+      <c r="D398" s="124"/>
+    </row>
+    <row r="399">
+      <c r="C399" s="123"/>
+      <c r="D399" s="124"/>
+    </row>
+    <row r="400">
+      <c r="C400" s="123"/>
+      <c r="D400" s="124"/>
+    </row>
+    <row r="401">
+      <c r="C401" s="123"/>
+      <c r="D401" s="124"/>
+    </row>
+    <row r="402">
+      <c r="C402" s="123"/>
+      <c r="D402" s="124"/>
+    </row>
+    <row r="403">
+      <c r="C403" s="123"/>
+      <c r="D403" s="124"/>
+    </row>
+    <row r="404">
+      <c r="C404" s="123"/>
+      <c r="D404" s="124"/>
+    </row>
+    <row r="405">
+      <c r="C405" s="123"/>
+      <c r="D405" s="124"/>
+    </row>
+    <row r="406">
+      <c r="C406" s="123"/>
+      <c r="D406" s="124"/>
+    </row>
+    <row r="407">
+      <c r="C407" s="123"/>
+      <c r="D407" s="124"/>
+    </row>
+    <row r="408">
+      <c r="C408" s="123"/>
+      <c r="D408" s="124"/>
+    </row>
+    <row r="409">
+      <c r="C409" s="123"/>
+      <c r="D409" s="124"/>
+    </row>
+    <row r="410">
+      <c r="C410" s="123"/>
+      <c r="D410" s="124"/>
+    </row>
+    <row r="411">
+      <c r="C411" s="123"/>
+      <c r="D411" s="124"/>
+    </row>
+    <row r="412">
+      <c r="C412" s="123"/>
+      <c r="D412" s="124"/>
+    </row>
+    <row r="413">
+      <c r="C413" s="123"/>
+      <c r="D413" s="124"/>
+    </row>
+    <row r="414">
+      <c r="C414" s="123"/>
+      <c r="D414" s="124"/>
+    </row>
+    <row r="415">
+      <c r="C415" s="123"/>
+      <c r="D415" s="124"/>
+    </row>
+    <row r="416">
+      <c r="C416" s="123"/>
+      <c r="D416" s="124"/>
+    </row>
+    <row r="417">
+      <c r="C417" s="123"/>
+      <c r="D417" s="124"/>
+    </row>
+    <row r="418">
+      <c r="C418" s="123"/>
+      <c r="D418" s="124"/>
+    </row>
+    <row r="419">
+      <c r="C419" s="123"/>
+      <c r="D419" s="124"/>
+    </row>
+    <row r="420">
+      <c r="C420" s="123"/>
+      <c r="D420" s="124"/>
+    </row>
+    <row r="421">
+      <c r="C421" s="123"/>
+      <c r="D421" s="124"/>
+    </row>
+    <row r="422">
+      <c r="C422" s="123"/>
+      <c r="D422" s="124"/>
+    </row>
+    <row r="423">
+      <c r="C423" s="123"/>
+      <c r="D423" s="124"/>
+    </row>
+    <row r="424">
+      <c r="C424" s="123"/>
+      <c r="D424" s="124"/>
+    </row>
+    <row r="425">
+      <c r="C425" s="123"/>
+      <c r="D425" s="124"/>
+    </row>
+    <row r="426">
+      <c r="C426" s="123"/>
+      <c r="D426" s="124"/>
+    </row>
+    <row r="427">
+      <c r="C427" s="123"/>
+      <c r="D427" s="124"/>
+    </row>
+    <row r="428">
+      <c r="C428" s="123"/>
+      <c r="D428" s="124"/>
+    </row>
+    <row r="429">
+      <c r="C429" s="123"/>
+      <c r="D429" s="124"/>
+    </row>
+    <row r="430">
+      <c r="C430" s="123"/>
+      <c r="D430" s="124"/>
+    </row>
+    <row r="431">
+      <c r="C431" s="123"/>
+      <c r="D431" s="124"/>
+    </row>
+    <row r="432">
+      <c r="C432" s="123"/>
+      <c r="D432" s="124"/>
+    </row>
+    <row r="433">
+      <c r="C433" s="123"/>
+      <c r="D433" s="124"/>
+    </row>
+    <row r="434">
+      <c r="C434" s="123"/>
+      <c r="D434" s="124"/>
+    </row>
+    <row r="435">
+      <c r="C435" s="123"/>
+      <c r="D435" s="124"/>
+    </row>
+    <row r="436">
+      <c r="C436" s="123"/>
+      <c r="D436" s="124"/>
+    </row>
+    <row r="437">
+      <c r="C437" s="123"/>
+      <c r="D437" s="124"/>
+    </row>
+    <row r="438">
+      <c r="C438" s="123"/>
+      <c r="D438" s="124"/>
+    </row>
+    <row r="439">
+      <c r="C439" s="123"/>
+      <c r="D439" s="124"/>
+    </row>
+    <row r="440">
+      <c r="C440" s="123"/>
+      <c r="D440" s="124"/>
+    </row>
+    <row r="441">
+      <c r="C441" s="123"/>
+      <c r="D441" s="124"/>
+    </row>
+    <row r="442">
+      <c r="C442" s="123"/>
+      <c r="D442" s="124"/>
+    </row>
+    <row r="443">
+      <c r="C443" s="123"/>
+      <c r="D443" s="124"/>
+    </row>
+    <row r="444">
+      <c r="C444" s="123"/>
+      <c r="D444" s="124"/>
+    </row>
+    <row r="445">
+      <c r="C445" s="123"/>
+      <c r="D445" s="124"/>
+    </row>
+    <row r="446">
+      <c r="C446" s="123"/>
+      <c r="D446" s="124"/>
+    </row>
+    <row r="447">
+      <c r="C447" s="123"/>
+      <c r="D447" s="124"/>
+    </row>
+    <row r="448">
+      <c r="C448" s="123"/>
+      <c r="D448" s="124"/>
+    </row>
+    <row r="449">
+      <c r="C449" s="123"/>
+      <c r="D449" s="124"/>
+    </row>
+    <row r="450">
+      <c r="C450" s="123"/>
+      <c r="D450" s="124"/>
+    </row>
+    <row r="451">
+      <c r="C451" s="123"/>
+      <c r="D451" s="124"/>
+    </row>
+    <row r="452">
+      <c r="C452" s="123"/>
+      <c r="D452" s="124"/>
+    </row>
+    <row r="453">
+      <c r="C453" s="123"/>
+      <c r="D453" s="124"/>
+    </row>
+    <row r="454">
+      <c r="C454" s="123"/>
+      <c r="D454" s="124"/>
+    </row>
+    <row r="455">
+      <c r="C455" s="123"/>
+      <c r="D455" s="124"/>
+    </row>
+    <row r="456">
+      <c r="C456" s="123"/>
+      <c r="D456" s="124"/>
+    </row>
+    <row r="457">
+      <c r="C457" s="123"/>
+      <c r="D457" s="124"/>
+    </row>
+    <row r="458">
+      <c r="C458" s="123"/>
+      <c r="D458" s="124"/>
+    </row>
+    <row r="459">
+      <c r="C459" s="123"/>
+      <c r="D459" s="124"/>
+    </row>
+    <row r="460">
+      <c r="C460" s="123"/>
+      <c r="D460" s="124"/>
+    </row>
+    <row r="461">
+      <c r="C461" s="123"/>
+      <c r="D461" s="124"/>
+    </row>
+    <row r="462">
+      <c r="C462" s="123"/>
+      <c r="D462" s="124"/>
+    </row>
+    <row r="463">
+      <c r="C463" s="123"/>
+      <c r="D463" s="124"/>
+    </row>
+    <row r="464">
+      <c r="C464" s="123"/>
+      <c r="D464" s="124"/>
+    </row>
+    <row r="465">
+      <c r="C465" s="123"/>
+      <c r="D465" s="124"/>
+    </row>
+    <row r="466">
+      <c r="C466" s="123"/>
+      <c r="D466" s="124"/>
+    </row>
+    <row r="467">
+      <c r="C467" s="123"/>
+      <c r="D467" s="124"/>
+    </row>
+    <row r="468">
+      <c r="C468" s="123"/>
+      <c r="D468" s="124"/>
+    </row>
+    <row r="469">
+      <c r="C469" s="123"/>
+      <c r="D469" s="124"/>
+    </row>
+    <row r="470">
+      <c r="C470" s="123"/>
+      <c r="D470" s="124"/>
+    </row>
+    <row r="471">
+      <c r="C471" s="123"/>
+      <c r="D471" s="124"/>
+    </row>
+    <row r="472">
+      <c r="C472" s="123"/>
+      <c r="D472" s="124"/>
+    </row>
+    <row r="473">
+      <c r="C473" s="123"/>
+      <c r="D473" s="124"/>
+    </row>
+    <row r="474">
+      <c r="C474" s="123"/>
+      <c r="D474" s="124"/>
+    </row>
+    <row r="475">
+      <c r="C475" s="123"/>
+      <c r="D475" s="124"/>
+    </row>
+    <row r="476">
+      <c r="C476" s="123"/>
+      <c r="D476" s="124"/>
+    </row>
+    <row r="477">
+      <c r="C477" s="123"/>
+      <c r="D477" s="124"/>
+    </row>
+    <row r="478">
+      <c r="C478" s="123"/>
+      <c r="D478" s="124"/>
+    </row>
+    <row r="479">
+      <c r="C479" s="123"/>
+      <c r="D479" s="124"/>
+    </row>
+    <row r="480">
+      <c r="C480" s="123"/>
+      <c r="D480" s="124"/>
+    </row>
+    <row r="481">
+      <c r="C481" s="123"/>
+      <c r="D481" s="124"/>
+    </row>
+    <row r="482">
+      <c r="C482" s="123"/>
+      <c r="D482" s="124"/>
+    </row>
+    <row r="483">
+      <c r="C483" s="123"/>
+      <c r="D483" s="124"/>
+    </row>
+    <row r="484">
+      <c r="C484" s="123"/>
+      <c r="D484" s="124"/>
+    </row>
+    <row r="485">
+      <c r="C485" s="123"/>
+      <c r="D485" s="124"/>
+    </row>
+    <row r="486">
+      <c r="C486" s="123"/>
+      <c r="D486" s="124"/>
+    </row>
+    <row r="487">
+      <c r="C487" s="123"/>
+      <c r="D487" s="124"/>
+    </row>
+    <row r="488">
+      <c r="C488" s="123"/>
+      <c r="D488" s="124"/>
+    </row>
+    <row r="489">
+      <c r="C489" s="123"/>
+      <c r="D489" s="124"/>
+    </row>
+    <row r="490">
+      <c r="C490" s="123"/>
+      <c r="D490" s="124"/>
+    </row>
+    <row r="491">
+      <c r="C491" s="123"/>
+      <c r="D491" s="124"/>
+    </row>
+    <row r="492">
+      <c r="C492" s="123"/>
+      <c r="D492" s="124"/>
+    </row>
+    <row r="493">
+      <c r="C493" s="123"/>
+      <c r="D493" s="124"/>
+    </row>
+    <row r="494">
+      <c r="C494" s="123"/>
+      <c r="D494" s="124"/>
+    </row>
+    <row r="495">
+      <c r="C495" s="123"/>
+      <c r="D495" s="124"/>
+    </row>
+    <row r="496">
+      <c r="C496" s="123"/>
+      <c r="D496" s="124"/>
+    </row>
+    <row r="497">
+      <c r="C497" s="123"/>
+      <c r="D497" s="124"/>
+    </row>
+    <row r="498">
+      <c r="C498" s="123"/>
+      <c r="D498" s="124"/>
+    </row>
+    <row r="499">
+      <c r="C499" s="123"/>
+      <c r="D499" s="124"/>
+    </row>
+    <row r="500">
+      <c r="C500" s="123"/>
+      <c r="D500" s="124"/>
+    </row>
+    <row r="501">
+      <c r="C501" s="123"/>
+      <c r="D501" s="124"/>
+    </row>
+    <row r="502">
+      <c r="C502" s="123"/>
+      <c r="D502" s="124"/>
+    </row>
+    <row r="503">
+      <c r="C503" s="123"/>
+      <c r="D503" s="124"/>
+    </row>
+    <row r="504">
+      <c r="C504" s="123"/>
+      <c r="D504" s="124"/>
+    </row>
+    <row r="505">
+      <c r="C505" s="123"/>
+      <c r="D505" s="124"/>
+    </row>
+    <row r="506">
+      <c r="C506" s="123"/>
+      <c r="D506" s="124"/>
+    </row>
+    <row r="507">
+      <c r="C507" s="123"/>
+      <c r="D507" s="124"/>
+    </row>
+    <row r="508">
+      <c r="C508" s="123"/>
+      <c r="D508" s="124"/>
+    </row>
+    <row r="509">
+      <c r="C509" s="123"/>
+      <c r="D509" s="124"/>
+    </row>
+    <row r="510">
+      <c r="C510" s="123"/>
+      <c r="D510" s="124"/>
+    </row>
+    <row r="511">
+      <c r="C511" s="123"/>
+      <c r="D511" s="124"/>
+    </row>
+    <row r="512">
+      <c r="C512" s="123"/>
+      <c r="D512" s="124"/>
+    </row>
+    <row r="513">
+      <c r="C513" s="123"/>
+      <c r="D513" s="124"/>
+    </row>
+    <row r="514">
+      <c r="C514" s="123"/>
+      <c r="D514" s="124"/>
+    </row>
+    <row r="515">
+      <c r="C515" s="123"/>
+      <c r="D515" s="124"/>
+    </row>
+    <row r="516">
+      <c r="C516" s="123"/>
+      <c r="D516" s="124"/>
+    </row>
+    <row r="517">
+      <c r="C517" s="123"/>
+      <c r="D517" s="124"/>
+    </row>
+    <row r="518">
+      <c r="C518" s="123"/>
+      <c r="D518" s="124"/>
+    </row>
+    <row r="519">
+      <c r="C519" s="123"/>
+      <c r="D519" s="124"/>
+    </row>
+    <row r="520">
+      <c r="C520" s="123"/>
+      <c r="D520" s="124"/>
+    </row>
+    <row r="521">
+      <c r="C521" s="123"/>
+      <c r="D521" s="124"/>
+    </row>
+    <row r="522">
+      <c r="C522" s="123"/>
+      <c r="D522" s="124"/>
+    </row>
+    <row r="523">
+      <c r="C523" s="123"/>
+      <c r="D523" s="124"/>
+    </row>
+    <row r="524">
+      <c r="C524" s="123"/>
+      <c r="D524" s="124"/>
+    </row>
+    <row r="525">
+      <c r="C525" s="123"/>
+      <c r="D525" s="124"/>
+    </row>
+    <row r="526">
+      <c r="C526" s="123"/>
+      <c r="D526" s="124"/>
+    </row>
+    <row r="527">
+      <c r="C527" s="123"/>
+      <c r="D527" s="124"/>
+    </row>
+    <row r="528">
+      <c r="C528" s="123"/>
+      <c r="D528" s="124"/>
+    </row>
+    <row r="529">
+      <c r="C529" s="123"/>
+      <c r="D529" s="124"/>
+    </row>
+    <row r="530">
+      <c r="C530" s="123"/>
+      <c r="D530" s="124"/>
+    </row>
+    <row r="531">
+      <c r="C531" s="123"/>
+      <c r="D531" s="124"/>
+    </row>
+    <row r="532">
+      <c r="C532" s="123"/>
+      <c r="D532" s="124"/>
+    </row>
+    <row r="533">
+      <c r="C533" s="123"/>
+      <c r="D533" s="124"/>
+    </row>
+    <row r="534">
+      <c r="C534" s="123"/>
+      <c r="D534" s="124"/>
+    </row>
+    <row r="535">
+      <c r="C535" s="123"/>
+      <c r="D535" s="124"/>
+    </row>
+    <row r="536">
+      <c r="C536" s="123"/>
+      <c r="D536" s="124"/>
+    </row>
+    <row r="537">
+      <c r="C537" s="123"/>
+      <c r="D537" s="124"/>
+    </row>
+    <row r="538">
+      <c r="C538" s="123"/>
+      <c r="D538" s="124"/>
+    </row>
+    <row r="539">
+      <c r="C539" s="123"/>
+      <c r="D539" s="124"/>
+    </row>
+    <row r="540">
+      <c r="C540" s="123"/>
+      <c r="D540" s="124"/>
+    </row>
+    <row r="541">
+      <c r="C541" s="123"/>
+      <c r="D541" s="124"/>
+    </row>
+    <row r="542">
+      <c r="C542" s="123"/>
+      <c r="D542" s="124"/>
+    </row>
+    <row r="543">
+      <c r="C543" s="123"/>
+      <c r="D543" s="124"/>
+    </row>
+    <row r="544">
+      <c r="C544" s="123"/>
+      <c r="D544" s="124"/>
+    </row>
+    <row r="545">
+      <c r="C545" s="123"/>
+      <c r="D545" s="124"/>
+    </row>
+    <row r="546">
+      <c r="C546" s="123"/>
+      <c r="D546" s="124"/>
+    </row>
+    <row r="547">
+      <c r="C547" s="123"/>
+      <c r="D547" s="124"/>
+    </row>
+    <row r="548">
+      <c r="C548" s="123"/>
+      <c r="D548" s="124"/>
+    </row>
+    <row r="549">
+      <c r="C549" s="123"/>
+      <c r="D549" s="124"/>
+    </row>
+    <row r="550">
+      <c r="C550" s="123"/>
+      <c r="D550" s="124"/>
+    </row>
+    <row r="551">
+      <c r="C551" s="123"/>
+      <c r="D551" s="124"/>
+    </row>
+    <row r="552">
+      <c r="C552" s="123"/>
+      <c r="D552" s="124"/>
+    </row>
+    <row r="553">
+      <c r="C553" s="123"/>
+      <c r="D553" s="124"/>
+    </row>
+    <row r="554">
+      <c r="C554" s="123"/>
+      <c r="D554" s="124"/>
+    </row>
+    <row r="555">
+      <c r="C555" s="123"/>
+      <c r="D555" s="124"/>
+    </row>
+    <row r="556">
+      <c r="C556" s="123"/>
+      <c r="D556" s="124"/>
+    </row>
+    <row r="557">
+      <c r="C557" s="123"/>
+      <c r="D557" s="124"/>
+    </row>
+    <row r="558">
+      <c r="C558" s="123"/>
+      <c r="D558" s="124"/>
+    </row>
+    <row r="559">
+      <c r="C559" s="123"/>
+      <c r="D559" s="124"/>
+    </row>
+    <row r="560">
+      <c r="C560" s="123"/>
+      <c r="D560" s="124"/>
+    </row>
+    <row r="561">
+      <c r="C561" s="123"/>
+      <c r="D561" s="124"/>
+    </row>
+    <row r="562">
+      <c r="C562" s="123"/>
+      <c r="D562" s="124"/>
+    </row>
+    <row r="563">
+      <c r="C563" s="123"/>
+      <c r="D563" s="124"/>
+    </row>
+    <row r="564">
+      <c r="C564" s="123"/>
+      <c r="D564" s="124"/>
+    </row>
+    <row r="565">
+      <c r="C565" s="123"/>
+      <c r="D565" s="124"/>
+    </row>
+    <row r="566">
+      <c r="C566" s="123"/>
+      <c r="D566" s="124"/>
+    </row>
+    <row r="567">
+      <c r="C567" s="123"/>
+      <c r="D567" s="124"/>
+    </row>
+    <row r="568">
+      <c r="C568" s="123"/>
+      <c r="D568" s="124"/>
+    </row>
+    <row r="569">
+      <c r="C569" s="123"/>
+      <c r="D569" s="124"/>
+    </row>
+    <row r="570">
+      <c r="C570" s="123"/>
+      <c r="D570" s="124"/>
+    </row>
+    <row r="571">
+      <c r="C571" s="123"/>
+      <c r="D571" s="124"/>
+    </row>
+    <row r="572">
+      <c r="C572" s="123"/>
+      <c r="D572" s="124"/>
+    </row>
+    <row r="573">
+      <c r="C573" s="123"/>
+      <c r="D573" s="124"/>
+    </row>
+    <row r="574">
+      <c r="C574" s="123"/>
+      <c r="D574" s="124"/>
+    </row>
+    <row r="575">
+      <c r="C575" s="123"/>
+      <c r="D575" s="124"/>
+    </row>
+    <row r="576">
+      <c r="C576" s="123"/>
+      <c r="D576" s="124"/>
+    </row>
+    <row r="577">
+      <c r="C577" s="123"/>
+      <c r="D577" s="124"/>
+    </row>
+    <row r="578">
+      <c r="C578" s="123"/>
+      <c r="D578" s="124"/>
+    </row>
+    <row r="579">
+      <c r="C579" s="123"/>
+      <c r="D579" s="124"/>
+    </row>
+    <row r="580">
+      <c r="C580" s="123"/>
+      <c r="D580" s="124"/>
+    </row>
+    <row r="581">
+      <c r="C581" s="123"/>
+      <c r="D581" s="124"/>
+    </row>
+    <row r="582">
+      <c r="C582" s="123"/>
+      <c r="D582" s="124"/>
+    </row>
+    <row r="583">
+      <c r="C583" s="123"/>
+      <c r="D583" s="124"/>
+    </row>
+    <row r="584">
+      <c r="C584" s="123"/>
+      <c r="D584" s="124"/>
+    </row>
+    <row r="585">
+      <c r="C585" s="123"/>
+      <c r="D585" s="124"/>
+    </row>
+    <row r="586">
+      <c r="C586" s="123"/>
+      <c r="D586" s="124"/>
+    </row>
+    <row r="587">
+      <c r="C587" s="123"/>
+      <c r="D587" s="124"/>
+    </row>
+    <row r="588">
+      <c r="C588" s="123"/>
+      <c r="D588" s="124"/>
+    </row>
+    <row r="589">
+      <c r="C589" s="123"/>
+      <c r="D589" s="124"/>
+    </row>
+    <row r="590">
+      <c r="C590" s="123"/>
+      <c r="D590" s="124"/>
+    </row>
+    <row r="591">
+      <c r="C591" s="123"/>
+      <c r="D591" s="124"/>
+    </row>
+    <row r="592">
+      <c r="C592" s="123"/>
+      <c r="D592" s="124"/>
+    </row>
+    <row r="593">
+      <c r="C593" s="123"/>
+      <c r="D593" s="124"/>
+    </row>
+    <row r="594">
+      <c r="C594" s="123"/>
+      <c r="D594" s="124"/>
+    </row>
+    <row r="595">
+      <c r="C595" s="123"/>
+      <c r="D595" s="124"/>
+    </row>
+    <row r="596">
+      <c r="C596" s="123"/>
+      <c r="D596" s="124"/>
+    </row>
+    <row r="597">
+      <c r="C597" s="123"/>
+      <c r="D597" s="124"/>
+    </row>
+    <row r="598">
+      <c r="C598" s="123"/>
+      <c r="D598" s="124"/>
+    </row>
+    <row r="599">
+      <c r="C599" s="123"/>
+      <c r="D599" s="124"/>
+    </row>
+    <row r="600">
+      <c r="C600" s="123"/>
+      <c r="D600" s="124"/>
+    </row>
+    <row r="601">
+      <c r="C601" s="123"/>
+      <c r="D601" s="124"/>
+    </row>
+    <row r="602">
+      <c r="C602" s="123"/>
+      <c r="D602" s="124"/>
+    </row>
+    <row r="603">
+      <c r="C603" s="123"/>
+      <c r="D603" s="124"/>
+    </row>
+    <row r="604">
+      <c r="C604" s="123"/>
+      <c r="D604" s="124"/>
+    </row>
+    <row r="605">
+      <c r="C605" s="123"/>
+      <c r="D605" s="124"/>
+    </row>
+    <row r="606">
+      <c r="C606" s="123"/>
+      <c r="D606" s="124"/>
+    </row>
+    <row r="607">
+      <c r="C607" s="123"/>
+      <c r="D607" s="124"/>
+    </row>
+    <row r="608">
+      <c r="C608" s="123"/>
+      <c r="D608" s="124"/>
+    </row>
+    <row r="609">
+      <c r="C609" s="123"/>
+      <c r="D609" s="124"/>
+    </row>
+    <row r="610">
+      <c r="C610" s="123"/>
+      <c r="D610" s="124"/>
+    </row>
+    <row r="611">
+      <c r="C611" s="123"/>
+      <c r="D611" s="124"/>
+    </row>
+    <row r="612">
+      <c r="C612" s="123"/>
+      <c r="D612" s="124"/>
+    </row>
+    <row r="613">
+      <c r="C613" s="123"/>
+      <c r="D613" s="124"/>
+    </row>
+    <row r="614">
+      <c r="C614" s="123"/>
+      <c r="D614" s="124"/>
+    </row>
+    <row r="615">
+      <c r="C615" s="123"/>
+      <c r="D615" s="124"/>
+    </row>
+    <row r="616">
+      <c r="C616" s="123"/>
+      <c r="D616" s="124"/>
+    </row>
+    <row r="617">
+      <c r="C617" s="123"/>
+      <c r="D617" s="124"/>
+    </row>
+    <row r="618">
+      <c r="C618" s="123"/>
+      <c r="D618" s="124"/>
+    </row>
+    <row r="619">
+      <c r="C619" s="123"/>
+      <c r="D619" s="124"/>
+    </row>
+    <row r="620">
+      <c r="C620" s="123"/>
+      <c r="D620" s="124"/>
+    </row>
+    <row r="621">
+      <c r="C621" s="123"/>
+      <c r="D621" s="124"/>
+    </row>
+    <row r="622">
+      <c r="C622" s="123"/>
+      <c r="D622" s="124"/>
+    </row>
+    <row r="623">
+      <c r="C623" s="123"/>
+      <c r="D623" s="124"/>
+    </row>
+    <row r="624">
+      <c r="C624" s="123"/>
+      <c r="D624" s="124"/>
+    </row>
+    <row r="625">
+      <c r="C625" s="123"/>
+      <c r="D625" s="124"/>
+    </row>
+    <row r="626">
+      <c r="C626" s="123"/>
+      <c r="D626" s="124"/>
+    </row>
+    <row r="627">
+      <c r="C627" s="123"/>
+      <c r="D627" s="124"/>
+    </row>
+    <row r="628">
+      <c r="C628" s="123"/>
+      <c r="D628" s="124"/>
+    </row>
+    <row r="629">
+      <c r="C629" s="123"/>
+      <c r="D629" s="124"/>
+    </row>
+    <row r="630">
+      <c r="C630" s="123"/>
+      <c r="D630" s="124"/>
+    </row>
+    <row r="631">
+      <c r="C631" s="123"/>
+      <c r="D631" s="124"/>
+    </row>
+    <row r="632">
+      <c r="C632" s="123"/>
+      <c r="D632" s="124"/>
+    </row>
+    <row r="633">
+      <c r="C633" s="123"/>
+      <c r="D633" s="124"/>
+    </row>
+    <row r="634">
+      <c r="C634" s="123"/>
+      <c r="D634" s="124"/>
+    </row>
+    <row r="635">
+      <c r="C635" s="123"/>
+      <c r="D635" s="124"/>
+    </row>
+    <row r="636">
+      <c r="C636" s="123"/>
+      <c r="D636" s="124"/>
+    </row>
+    <row r="637">
+      <c r="C637" s="123"/>
+      <c r="D637" s="124"/>
+    </row>
+    <row r="638">
+      <c r="C638" s="123"/>
+      <c r="D638" s="124"/>
+    </row>
+    <row r="639">
+      <c r="C639" s="123"/>
+      <c r="D639" s="124"/>
+    </row>
+    <row r="640">
+      <c r="C640" s="123"/>
+      <c r="D640" s="124"/>
+    </row>
+    <row r="641">
+      <c r="C641" s="123"/>
+      <c r="D641" s="124"/>
+    </row>
+    <row r="642">
+      <c r="C642" s="123"/>
+      <c r="D642" s="124"/>
+    </row>
+    <row r="643">
+      <c r="C643" s="123"/>
+      <c r="D643" s="124"/>
+    </row>
+    <row r="644">
+      <c r="C644" s="123"/>
+      <c r="D644" s="124"/>
+    </row>
+    <row r="645">
+      <c r="C645" s="123"/>
+      <c r="D645" s="124"/>
+    </row>
+    <row r="646">
+      <c r="C646" s="123"/>
+      <c r="D646" s="124"/>
+    </row>
+    <row r="647">
+      <c r="C647" s="123"/>
+      <c r="D647" s="124"/>
+    </row>
+    <row r="648">
+      <c r="C648" s="123"/>
+      <c r="D648" s="124"/>
+    </row>
+    <row r="649">
+      <c r="C649" s="123"/>
+      <c r="D649" s="124"/>
+    </row>
+    <row r="650">
+      <c r="C650" s="123"/>
+      <c r="D650" s="124"/>
+    </row>
+    <row r="651">
+      <c r="C651" s="123"/>
+      <c r="D651" s="124"/>
+    </row>
+    <row r="652">
+      <c r="C652" s="123"/>
+      <c r="D652" s="124"/>
+    </row>
+    <row r="653">
+      <c r="C653" s="123"/>
+      <c r="D653" s="124"/>
+    </row>
+    <row r="654">
+      <c r="C654" s="123"/>
+      <c r="D654" s="124"/>
+    </row>
+    <row r="655">
+      <c r="C655" s="123"/>
+      <c r="D655" s="124"/>
+    </row>
+    <row r="656">
+      <c r="C656" s="123"/>
+      <c r="D656" s="124"/>
+    </row>
+    <row r="657">
+      <c r="C657" s="123"/>
+      <c r="D657" s="124"/>
+    </row>
+    <row r="658">
+      <c r="C658" s="123"/>
+      <c r="D658" s="124"/>
+    </row>
+    <row r="659">
+      <c r="C659" s="123"/>
+      <c r="D659" s="124"/>
+    </row>
+    <row r="660">
+      <c r="C660" s="123"/>
+      <c r="D660" s="124"/>
+    </row>
+    <row r="661">
+      <c r="C661" s="123"/>
+      <c r="D661" s="124"/>
+    </row>
+    <row r="662">
+      <c r="C662" s="123"/>
+      <c r="D662" s="124"/>
+    </row>
+    <row r="663">
+      <c r="C663" s="123"/>
+      <c r="D663" s="124"/>
+    </row>
+    <row r="664">
+      <c r="C664" s="123"/>
+      <c r="D664" s="124"/>
+    </row>
+    <row r="665">
+      <c r="C665" s="123"/>
+      <c r="D665" s="124"/>
+    </row>
+    <row r="666">
+      <c r="C666" s="123"/>
+      <c r="D666" s="124"/>
+    </row>
+    <row r="667">
+      <c r="C667" s="123"/>
+      <c r="D667" s="124"/>
+    </row>
+    <row r="668">
+      <c r="C668" s="123"/>
+      <c r="D668" s="124"/>
+    </row>
+    <row r="669">
+      <c r="C669" s="123"/>
+      <c r="D669" s="124"/>
+    </row>
+    <row r="670">
+      <c r="C670" s="123"/>
+      <c r="D670" s="124"/>
+    </row>
+    <row r="671">
+      <c r="C671" s="123"/>
+      <c r="D671" s="124"/>
+    </row>
+    <row r="672">
+      <c r="C672" s="123"/>
+      <c r="D672" s="124"/>
+    </row>
+    <row r="673">
+      <c r="C673" s="123"/>
+      <c r="D673" s="124"/>
+    </row>
+    <row r="674">
+      <c r="C674" s="123"/>
+      <c r="D674" s="124"/>
+    </row>
+    <row r="675">
+      <c r="C675" s="123"/>
+      <c r="D675" s="124"/>
+    </row>
+    <row r="676">
+      <c r="C676" s="123"/>
+      <c r="D676" s="124"/>
+    </row>
+    <row r="677">
+      <c r="C677" s="123"/>
+      <c r="D677" s="124"/>
+    </row>
+    <row r="678">
+      <c r="C678" s="123"/>
+      <c r="D678" s="124"/>
+    </row>
+    <row r="679">
+      <c r="C679" s="123"/>
+      <c r="D679" s="124"/>
+    </row>
+    <row r="680">
+      <c r="C680" s="123"/>
+      <c r="D680" s="124"/>
+    </row>
+    <row r="681">
+      <c r="C681" s="123"/>
+      <c r="D681" s="124"/>
+    </row>
+    <row r="682">
+      <c r="C682" s="123"/>
+      <c r="D682" s="124"/>
+    </row>
+    <row r="683">
+      <c r="C683" s="123"/>
+      <c r="D683" s="124"/>
+    </row>
+    <row r="684">
+      <c r="C684" s="123"/>
+      <c r="D684" s="124"/>
+    </row>
+    <row r="685">
+      <c r="C685" s="123"/>
+      <c r="D685" s="124"/>
+    </row>
+    <row r="686">
+      <c r="C686" s="123"/>
+      <c r="D686" s="124"/>
+    </row>
+    <row r="687">
+      <c r="C687" s="123"/>
+      <c r="D687" s="124"/>
+    </row>
+    <row r="688">
+      <c r="C688" s="123"/>
+      <c r="D688" s="124"/>
+    </row>
+    <row r="689">
+      <c r="C689" s="123"/>
+      <c r="D689" s="124"/>
+    </row>
+    <row r="690">
+      <c r="C690" s="123"/>
+      <c r="D690" s="124"/>
+    </row>
+    <row r="691">
+      <c r="C691" s="123"/>
+      <c r="D691" s="124"/>
+    </row>
+    <row r="692">
+      <c r="C692" s="123"/>
+      <c r="D692" s="124"/>
+    </row>
+    <row r="693">
+      <c r="C693" s="123"/>
+      <c r="D693" s="124"/>
+    </row>
+    <row r="694">
+      <c r="C694" s="123"/>
+      <c r="D694" s="124"/>
+    </row>
+    <row r="695">
+      <c r="C695" s="123"/>
+      <c r="D695" s="124"/>
+    </row>
+    <row r="696">
+      <c r="C696" s="123"/>
+      <c r="D696" s="124"/>
+    </row>
+    <row r="697">
+      <c r="C697" s="123"/>
+      <c r="D697" s="124"/>
+    </row>
+    <row r="698">
+      <c r="C698" s="123"/>
+      <c r="D698" s="124"/>
+    </row>
+    <row r="699">
+      <c r="C699" s="123"/>
+      <c r="D699" s="124"/>
+    </row>
+    <row r="700">
+      <c r="C700" s="123"/>
+      <c r="D700" s="124"/>
+    </row>
+    <row r="701">
+      <c r="C701" s="123"/>
+      <c r="D701" s="124"/>
+    </row>
+    <row r="702">
+      <c r="C702" s="123"/>
+      <c r="D702" s="124"/>
+    </row>
+    <row r="703">
+      <c r="C703" s="123"/>
+      <c r="D703" s="124"/>
+    </row>
+    <row r="704">
+      <c r="C704" s="123"/>
+      <c r="D704" s="124"/>
+    </row>
+    <row r="705">
+      <c r="C705" s="123"/>
+      <c r="D705" s="124"/>
+    </row>
+    <row r="706">
+      <c r="C706" s="123"/>
+      <c r="D706" s="124"/>
+    </row>
+    <row r="707">
+      <c r="C707" s="123"/>
+      <c r="D707" s="124"/>
+    </row>
+    <row r="708">
+      <c r="C708" s="123"/>
+      <c r="D708" s="124"/>
+    </row>
+    <row r="709">
+      <c r="C709" s="123"/>
+      <c r="D709" s="124"/>
+    </row>
+    <row r="710">
+      <c r="C710" s="123"/>
+      <c r="D710" s="124"/>
+    </row>
+    <row r="711">
+      <c r="C711" s="123"/>
+      <c r="D711" s="124"/>
+    </row>
+    <row r="712">
+      <c r="C712" s="123"/>
+      <c r="D712" s="124"/>
+    </row>
+    <row r="713">
+      <c r="C713" s="123"/>
+      <c r="D713" s="124"/>
+    </row>
+    <row r="714">
+      <c r="C714" s="123"/>
+      <c r="D714" s="124"/>
+    </row>
+    <row r="715">
+      <c r="C715" s="123"/>
+      <c r="D715" s="124"/>
+    </row>
+    <row r="716">
+      <c r="C716" s="123"/>
+      <c r="D716" s="124"/>
+    </row>
+    <row r="717">
+      <c r="C717" s="123"/>
+      <c r="D717" s="124"/>
+    </row>
+    <row r="718">
+      <c r="C718" s="123"/>
+      <c r="D718" s="124"/>
+    </row>
+    <row r="719">
+      <c r="C719" s="123"/>
+      <c r="D719" s="124"/>
+    </row>
+    <row r="720">
+      <c r="C720" s="123"/>
+      <c r="D720" s="124"/>
+    </row>
+    <row r="721">
+      <c r="C721" s="123"/>
+      <c r="D721" s="124"/>
+    </row>
+    <row r="722">
+      <c r="C722" s="123"/>
+      <c r="D722" s="124"/>
+    </row>
+    <row r="723">
+      <c r="C723" s="123"/>
+      <c r="D723" s="124"/>
+    </row>
+    <row r="724">
+      <c r="C724" s="123"/>
+      <c r="D724" s="124"/>
+    </row>
+    <row r="725">
+      <c r="C725" s="123"/>
+      <c r="D725" s="124"/>
+    </row>
+    <row r="726">
+      <c r="C726" s="123"/>
+      <c r="D726" s="124"/>
+    </row>
+    <row r="727">
+      <c r="C727" s="123"/>
+      <c r="D727" s="124"/>
+    </row>
+    <row r="728">
+      <c r="C728" s="123"/>
+      <c r="D728" s="124"/>
+    </row>
+    <row r="729">
+      <c r="C729" s="123"/>
+      <c r="D729" s="124"/>
+    </row>
+    <row r="730">
+      <c r="C730" s="123"/>
+      <c r="D730" s="124"/>
+    </row>
+    <row r="731">
+      <c r="C731" s="123"/>
+      <c r="D731" s="124"/>
+    </row>
+    <row r="732">
+      <c r="C732" s="123"/>
+      <c r="D732" s="124"/>
+    </row>
+    <row r="733">
+      <c r="C733" s="123"/>
+      <c r="D733" s="124"/>
+    </row>
+    <row r="734">
+      <c r="C734" s="123"/>
+      <c r="D734" s="124"/>
+    </row>
+    <row r="735">
+      <c r="C735" s="123"/>
+      <c r="D735" s="124"/>
+    </row>
+    <row r="736">
+      <c r="C736" s="123"/>
+      <c r="D736" s="124"/>
+    </row>
+    <row r="737">
+      <c r="C737" s="123"/>
+      <c r="D737" s="124"/>
+    </row>
+    <row r="738">
+      <c r="C738" s="123"/>
+      <c r="D738" s="124"/>
+    </row>
+    <row r="739">
+      <c r="C739" s="123"/>
+      <c r="D739" s="124"/>
+    </row>
+    <row r="740">
+      <c r="C740" s="123"/>
+      <c r="D740" s="124"/>
+    </row>
+    <row r="741">
+      <c r="C741" s="123"/>
+      <c r="D741" s="124"/>
+    </row>
+    <row r="742">
+      <c r="C742" s="123"/>
+      <c r="D742" s="124"/>
+    </row>
+    <row r="743">
+      <c r="C743" s="123"/>
+      <c r="D743" s="124"/>
+    </row>
+    <row r="744">
+      <c r="C744" s="123"/>
+      <c r="D744" s="124"/>
+    </row>
+    <row r="745">
+      <c r="C745" s="123"/>
+      <c r="D745" s="124"/>
+    </row>
+    <row r="746">
+      <c r="C746" s="123"/>
+      <c r="D746" s="124"/>
+    </row>
+    <row r="747">
+      <c r="C747" s="123"/>
+      <c r="D747" s="124"/>
+    </row>
+    <row r="748">
+      <c r="C748" s="123"/>
+      <c r="D748" s="124"/>
+    </row>
+    <row r="749">
+      <c r="C749" s="123"/>
+      <c r="D749" s="124"/>
+    </row>
+    <row r="750">
+      <c r="C750" s="123"/>
+      <c r="D750" s="124"/>
+    </row>
+    <row r="751">
+      <c r="C751" s="123"/>
+      <c r="D751" s="124"/>
+    </row>
+    <row r="752">
+      <c r="C752" s="123"/>
+      <c r="D752" s="124"/>
+    </row>
+    <row r="753">
+      <c r="C753" s="123"/>
+      <c r="D753" s="124"/>
+    </row>
+    <row r="754">
+      <c r="C754" s="123"/>
+      <c r="D754" s="124"/>
+    </row>
+    <row r="755">
+      <c r="C755" s="123"/>
+      <c r="D755" s="124"/>
+    </row>
+    <row r="756">
+      <c r="C756" s="123"/>
+      <c r="D756" s="124"/>
+    </row>
+    <row r="757">
+      <c r="C757" s="123"/>
+      <c r="D757" s="124"/>
+    </row>
+    <row r="758">
+      <c r="C758" s="123"/>
+      <c r="D758" s="124"/>
+    </row>
+    <row r="759">
+      <c r="C759" s="123"/>
+      <c r="D759" s="124"/>
+    </row>
+    <row r="760">
+      <c r="C760" s="123"/>
+      <c r="D760" s="124"/>
+    </row>
+    <row r="761">
+      <c r="C761" s="123"/>
+      <c r="D761" s="124"/>
+    </row>
+    <row r="762">
+      <c r="C762" s="123"/>
+      <c r="D762" s="124"/>
+    </row>
+    <row r="763">
+      <c r="C763" s="123"/>
+      <c r="D763" s="124"/>
+    </row>
+    <row r="764">
+      <c r="C764" s="123"/>
+      <c r="D764" s="124"/>
+    </row>
+    <row r="765">
+      <c r="C765" s="123"/>
+      <c r="D765" s="124"/>
+    </row>
+    <row r="766">
+      <c r="C766" s="123"/>
+      <c r="D766" s="124"/>
+    </row>
+    <row r="767">
+      <c r="C767" s="123"/>
+      <c r="D767" s="124"/>
+    </row>
+    <row r="768">
+      <c r="C768" s="123"/>
+      <c r="D768" s="124"/>
+    </row>
+    <row r="769">
+      <c r="C769" s="123"/>
+      <c r="D769" s="124"/>
+    </row>
+    <row r="770">
+      <c r="C770" s="123"/>
+      <c r="D770" s="124"/>
+    </row>
+    <row r="771">
+      <c r="C771" s="123"/>
+      <c r="D771" s="124"/>
+    </row>
+    <row r="772">
+      <c r="C772" s="123"/>
+      <c r="D772" s="124"/>
+    </row>
+    <row r="773">
+      <c r="C773" s="123"/>
+      <c r="D773" s="124"/>
+    </row>
+    <row r="774">
+      <c r="C774" s="123"/>
+      <c r="D774" s="124"/>
+    </row>
+    <row r="775">
+      <c r="C775" s="123"/>
+      <c r="D775" s="124"/>
+    </row>
+    <row r="776">
+      <c r="C776" s="123"/>
+      <c r="D776" s="124"/>
+    </row>
+    <row r="777">
+      <c r="C777" s="123"/>
+      <c r="D777" s="124"/>
+    </row>
+    <row r="778">
+      <c r="C778" s="123"/>
+      <c r="D778" s="124"/>
+    </row>
+    <row r="779">
+      <c r="C779" s="123"/>
+      <c r="D779" s="124"/>
+    </row>
+    <row r="780">
+      <c r="C780" s="123"/>
+      <c r="D780" s="124"/>
+    </row>
+    <row r="781">
+      <c r="C781" s="123"/>
+      <c r="D781" s="124"/>
+    </row>
+    <row r="782">
+      <c r="C782" s="123"/>
+      <c r="D782" s="124"/>
+    </row>
+    <row r="783">
+      <c r="C783" s="123"/>
+      <c r="D783" s="124"/>
+    </row>
+    <row r="784">
+      <c r="C784" s="123"/>
+      <c r="D784" s="124"/>
+    </row>
+    <row r="785">
+      <c r="C785" s="123"/>
+      <c r="D785" s="124"/>
+    </row>
+    <row r="786">
+      <c r="C786" s="123"/>
+      <c r="D786" s="124"/>
+    </row>
+    <row r="787">
+      <c r="C787" s="123"/>
+      <c r="D787" s="124"/>
+    </row>
+    <row r="788">
+      <c r="C788" s="123"/>
+      <c r="D788" s="124"/>
+    </row>
+    <row r="789">
+      <c r="C789" s="123"/>
+      <c r="D789" s="124"/>
+    </row>
+    <row r="790">
+      <c r="C790" s="123"/>
+      <c r="D790" s="124"/>
+    </row>
+    <row r="791">
+      <c r="C791" s="123"/>
+      <c r="D791" s="124"/>
+    </row>
+    <row r="792">
+      <c r="C792" s="123"/>
+      <c r="D792" s="124"/>
+    </row>
+    <row r="793">
+      <c r="C793" s="123"/>
+      <c r="D793" s="124"/>
+    </row>
+    <row r="794">
+      <c r="C794" s="123"/>
+      <c r="D794" s="124"/>
+    </row>
+    <row r="795">
+      <c r="C795" s="123"/>
+      <c r="D795" s="124"/>
+    </row>
+    <row r="796">
+      <c r="C796" s="123"/>
+      <c r="D796" s="124"/>
+    </row>
+    <row r="797">
+      <c r="C797" s="123"/>
+      <c r="D797" s="124"/>
+    </row>
+    <row r="798">
+      <c r="C798" s="123"/>
+      <c r="D798" s="124"/>
+    </row>
+    <row r="799">
+      <c r="C799" s="123"/>
+      <c r="D799" s="124"/>
+    </row>
+    <row r="800">
+      <c r="C800" s="123"/>
+      <c r="D800" s="124"/>
+    </row>
+    <row r="801">
+      <c r="C801" s="123"/>
+      <c r="D801" s="124"/>
+    </row>
+    <row r="802">
+      <c r="C802" s="123"/>
+      <c r="D802" s="124"/>
+    </row>
+    <row r="803">
+      <c r="C803" s="123"/>
+      <c r="D803" s="124"/>
+    </row>
+    <row r="804">
+      <c r="C804" s="123"/>
+      <c r="D804" s="124"/>
+    </row>
+    <row r="805">
+      <c r="C805" s="123"/>
+      <c r="D805" s="124"/>
+    </row>
+    <row r="806">
+      <c r="C806" s="123"/>
+      <c r="D806" s="124"/>
+    </row>
+    <row r="807">
+      <c r="C807" s="123"/>
+      <c r="D807" s="124"/>
+    </row>
+    <row r="808">
+      <c r="C808" s="123"/>
+      <c r="D808" s="124"/>
+    </row>
+    <row r="809">
+      <c r="C809" s="123"/>
+      <c r="D809" s="124"/>
+    </row>
+    <row r="810">
+      <c r="C810" s="123"/>
+      <c r="D810" s="124"/>
+    </row>
+    <row r="811">
+      <c r="C811" s="123"/>
+      <c r="D811" s="124"/>
+    </row>
+    <row r="812">
+      <c r="C812" s="123"/>
+      <c r="D812" s="124"/>
+    </row>
+    <row r="813">
+      <c r="C813" s="123"/>
+      <c r="D813" s="124"/>
+    </row>
+    <row r="814">
+      <c r="C814" s="123"/>
+      <c r="D814" s="124"/>
+    </row>
+    <row r="815">
+      <c r="C815" s="123"/>
+      <c r="D815" s="124"/>
+    </row>
+    <row r="816">
+      <c r="C816" s="123"/>
+      <c r="D816" s="124"/>
+    </row>
+    <row r="817">
+      <c r="C817" s="123"/>
+      <c r="D817" s="124"/>
+    </row>
+    <row r="818">
+      <c r="C818" s="123"/>
+      <c r="D818" s="124"/>
+    </row>
+    <row r="819">
+      <c r="C819" s="123"/>
+      <c r="D819" s="124"/>
+    </row>
+    <row r="820">
+      <c r="C820" s="123"/>
+      <c r="D820" s="124"/>
+    </row>
+    <row r="821">
+      <c r="C821" s="123"/>
+      <c r="D821" s="124"/>
+    </row>
+    <row r="822">
+      <c r="C822" s="123"/>
+      <c r="D822" s="124"/>
+    </row>
+    <row r="823">
+      <c r="C823" s="123"/>
+      <c r="D823" s="124"/>
+    </row>
+    <row r="824">
+      <c r="C824" s="123"/>
+      <c r="D824" s="124"/>
+    </row>
+    <row r="825">
+      <c r="C825" s="123"/>
+      <c r="D825" s="124"/>
+    </row>
+    <row r="826">
+      <c r="C826" s="123"/>
+      <c r="D826" s="124"/>
+    </row>
+    <row r="827">
+      <c r="C827" s="123"/>
+      <c r="D827" s="124"/>
+    </row>
+    <row r="828">
+      <c r="C828" s="123"/>
+      <c r="D828" s="124"/>
+    </row>
+    <row r="829">
+      <c r="C829" s="123"/>
+      <c r="D829" s="124"/>
+    </row>
+    <row r="830">
+      <c r="C830" s="123"/>
+      <c r="D830" s="124"/>
+    </row>
+    <row r="831">
+      <c r="C831" s="123"/>
+      <c r="D831" s="124"/>
+    </row>
+    <row r="832">
+      <c r="C832" s="123"/>
+      <c r="D832" s="124"/>
+    </row>
+    <row r="833">
+      <c r="C833" s="123"/>
+      <c r="D833" s="124"/>
+    </row>
+    <row r="834">
+      <c r="C834" s="123"/>
+      <c r="D834" s="124"/>
+    </row>
+    <row r="835">
+      <c r="C835" s="123"/>
+      <c r="D835" s="124"/>
+    </row>
+    <row r="836">
+      <c r="C836" s="123"/>
+      <c r="D836" s="124"/>
+    </row>
+    <row r="837">
+      <c r="C837" s="123"/>
+      <c r="D837" s="124"/>
+    </row>
+    <row r="838">
+      <c r="C838" s="123"/>
+      <c r="D838" s="124"/>
+    </row>
+    <row r="839">
+      <c r="C839" s="123"/>
+      <c r="D839" s="124"/>
+    </row>
+    <row r="840">
+      <c r="C840" s="123"/>
+      <c r="D840" s="124"/>
+    </row>
+    <row r="841">
+      <c r="C841" s="123"/>
+      <c r="D841" s="124"/>
+    </row>
+    <row r="842">
+      <c r="C842" s="123"/>
+      <c r="D842" s="124"/>
+    </row>
+    <row r="843">
+      <c r="C843" s="123"/>
+      <c r="D843" s="124"/>
+    </row>
+    <row r="844">
+      <c r="C844" s="123"/>
+      <c r="D844" s="124"/>
+    </row>
+    <row r="845">
+      <c r="C845" s="123"/>
+      <c r="D845" s="124"/>
+    </row>
+    <row r="846">
+      <c r="C846" s="123"/>
+      <c r="D846" s="124"/>
+    </row>
+    <row r="847">
+      <c r="C847" s="123"/>
+      <c r="D847" s="124"/>
+    </row>
+    <row r="848">
+      <c r="C848" s="123"/>
+      <c r="D848" s="124"/>
+    </row>
+    <row r="849">
+      <c r="C849" s="123"/>
+      <c r="D849" s="124"/>
+    </row>
+    <row r="850">
+      <c r="C850" s="123"/>
+      <c r="D850" s="124"/>
+    </row>
+    <row r="851">
+      <c r="C851" s="123"/>
+      <c r="D851" s="124"/>
+    </row>
+    <row r="852">
+      <c r="C852" s="123"/>
+      <c r="D852" s="124"/>
+    </row>
+    <row r="853">
+      <c r="C853" s="123"/>
+      <c r="D853" s="124"/>
+    </row>
+    <row r="854">
+      <c r="C854" s="123"/>
+      <c r="D854" s="124"/>
+    </row>
+    <row r="855">
+      <c r="C855" s="123"/>
+      <c r="D855" s="124"/>
+    </row>
+    <row r="856">
+      <c r="C856" s="123"/>
+      <c r="D856" s="124"/>
+    </row>
+    <row r="857">
+      <c r="C857" s="123"/>
+      <c r="D857" s="124"/>
+    </row>
+    <row r="858">
+      <c r="C858" s="123"/>
+      <c r="D858" s="124"/>
+    </row>
+    <row r="859">
+      <c r="C859" s="123"/>
+      <c r="D859" s="124"/>
+    </row>
+    <row r="860">
+      <c r="C860" s="123"/>
+      <c r="D860" s="124"/>
+    </row>
+    <row r="861">
+      <c r="C861" s="123"/>
+      <c r="D861" s="124"/>
+    </row>
+    <row r="862">
+      <c r="C862" s="123"/>
+      <c r="D862" s="124"/>
+    </row>
+    <row r="863">
+      <c r="C863" s="123"/>
+      <c r="D863" s="124"/>
+    </row>
+    <row r="864">
+      <c r="C864" s="123"/>
+      <c r="D864" s="124"/>
+    </row>
+    <row r="865">
+      <c r="C865" s="123"/>
+      <c r="D865" s="124"/>
+    </row>
+    <row r="866">
+      <c r="C866" s="123"/>
+      <c r="D866" s="124"/>
+    </row>
+    <row r="867">
+      <c r="C867" s="123"/>
+      <c r="D867" s="124"/>
+    </row>
+    <row r="868">
+      <c r="C868" s="123"/>
+      <c r="D868" s="124"/>
+    </row>
+    <row r="869">
+      <c r="C869" s="123"/>
+      <c r="D869" s="124"/>
+    </row>
+    <row r="870">
+      <c r="C870" s="123"/>
+      <c r="D870" s="124"/>
+    </row>
+    <row r="871">
+      <c r="C871" s="123"/>
+      <c r="D871" s="124"/>
+    </row>
+    <row r="872">
+      <c r="C872" s="123"/>
+      <c r="D872" s="124"/>
+    </row>
+    <row r="873">
+      <c r="C873" s="123"/>
+      <c r="D873" s="124"/>
+    </row>
+    <row r="874">
+      <c r="C874" s="123"/>
+      <c r="D874" s="124"/>
+    </row>
+    <row r="875">
+      <c r="C875" s="123"/>
+      <c r="D875" s="124"/>
+    </row>
+    <row r="876">
+      <c r="C876" s="123"/>
+      <c r="D876" s="124"/>
+    </row>
+    <row r="877">
+      <c r="C877" s="123"/>
+      <c r="D877" s="124"/>
+    </row>
+    <row r="878">
+      <c r="C878" s="123"/>
+      <c r="D878" s="124"/>
+    </row>
+    <row r="879">
+      <c r="C879" s="123"/>
+      <c r="D879" s="124"/>
+    </row>
+    <row r="880">
+      <c r="C880" s="123"/>
+      <c r="D880" s="124"/>
+    </row>
+    <row r="881">
+      <c r="C881" s="123"/>
+      <c r="D881" s="124"/>
+    </row>
+    <row r="882">
+      <c r="C882" s="123"/>
+      <c r="D882" s="124"/>
+    </row>
+    <row r="883">
+      <c r="C883" s="123"/>
+      <c r="D883" s="124"/>
+    </row>
+    <row r="884">
+      <c r="C884" s="123"/>
+      <c r="D884" s="124"/>
+    </row>
+    <row r="885">
+      <c r="C885" s="123"/>
+      <c r="D885" s="124"/>
+    </row>
+    <row r="886">
+      <c r="C886" s="123"/>
+      <c r="D886" s="124"/>
+    </row>
+    <row r="887">
+      <c r="C887" s="123"/>
+      <c r="D887" s="124"/>
+    </row>
+    <row r="888">
+      <c r="C888" s="123"/>
+      <c r="D888" s="124"/>
+    </row>
+    <row r="889">
+      <c r="C889" s="123"/>
+      <c r="D889" s="124"/>
+    </row>
+    <row r="890">
+      <c r="C890" s="123"/>
+      <c r="D890" s="124"/>
+    </row>
+    <row r="891">
+      <c r="C891" s="123"/>
+      <c r="D891" s="124"/>
+    </row>
+    <row r="892">
+      <c r="C892" s="123"/>
+      <c r="D892" s="124"/>
+    </row>
+    <row r="893">
+      <c r="C893" s="123"/>
+      <c r="D893" s="124"/>
+    </row>
+    <row r="894">
+      <c r="C894" s="123"/>
+      <c r="D894" s="124"/>
+    </row>
+    <row r="895">
+      <c r="C895" s="123"/>
+      <c r="D895" s="124"/>
+    </row>
+    <row r="896">
+      <c r="C896" s="123"/>
+      <c r="D896" s="124"/>
+    </row>
+    <row r="897">
+      <c r="C897" s="123"/>
+      <c r="D897" s="124"/>
+    </row>
+    <row r="898">
+      <c r="C898" s="123"/>
+      <c r="D898" s="124"/>
+    </row>
+    <row r="899">
+      <c r="C899" s="123"/>
+      <c r="D899" s="124"/>
+    </row>
+    <row r="900">
+      <c r="C900" s="123"/>
+      <c r="D900" s="124"/>
+    </row>
+    <row r="901">
+      <c r="C901" s="123"/>
+      <c r="D901" s="124"/>
+    </row>
+    <row r="902">
+      <c r="C902" s="123"/>
+      <c r="D902" s="124"/>
+    </row>
+    <row r="903">
+      <c r="C903" s="123"/>
+      <c r="D903" s="124"/>
+    </row>
+    <row r="904">
+      <c r="C904" s="123"/>
+      <c r="D904" s="124"/>
+    </row>
+    <row r="905">
+      <c r="C905" s="123"/>
+      <c r="D905" s="124"/>
+    </row>
+    <row r="906">
+      <c r="C906" s="123"/>
+      <c r="D906" s="124"/>
+    </row>
+    <row r="907">
+      <c r="C907" s="123"/>
+      <c r="D907" s="124"/>
+    </row>
+    <row r="908">
+      <c r="C908" s="123"/>
+      <c r="D908" s="124"/>
+    </row>
+    <row r="909">
+      <c r="C909" s="123"/>
+      <c r="D909" s="124"/>
+    </row>
+    <row r="910">
+      <c r="C910" s="123"/>
+      <c r="D910" s="124"/>
+    </row>
+    <row r="911">
+      <c r="C911" s="123"/>
+      <c r="D911" s="124"/>
+    </row>
+    <row r="912">
+      <c r="C912" s="123"/>
+      <c r="D912" s="124"/>
+    </row>
+    <row r="913">
+      <c r="C913" s="123"/>
+      <c r="D913" s="124"/>
+    </row>
+    <row r="914">
+      <c r="C914" s="123"/>
+      <c r="D914" s="124"/>
+    </row>
+    <row r="915">
+      <c r="C915" s="123"/>
+      <c r="D915" s="124"/>
+    </row>
+    <row r="916">
+      <c r="C916" s="123"/>
+      <c r="D916" s="124"/>
+    </row>
+    <row r="917">
+      <c r="C917" s="123"/>
+      <c r="D917" s="124"/>
+    </row>
+    <row r="918">
+      <c r="C918" s="123"/>
+      <c r="D918" s="124"/>
+    </row>
+    <row r="919">
+      <c r="C919" s="123"/>
+      <c r="D919" s="124"/>
+    </row>
+    <row r="920">
+      <c r="C920" s="123"/>
+      <c r="D920" s="124"/>
+    </row>
+    <row r="921">
+      <c r="C921" s="123"/>
+      <c r="D921" s="124"/>
+    </row>
+    <row r="922">
+      <c r="C922" s="123"/>
+      <c r="D922" s="124"/>
+    </row>
+    <row r="923">
+      <c r="C923" s="123"/>
+      <c r="D923" s="124"/>
+    </row>
+    <row r="924">
+      <c r="C924" s="123"/>
+      <c r="D924" s="124"/>
+    </row>
+    <row r="925">
+      <c r="C925" s="123"/>
+      <c r="D925" s="124"/>
+    </row>
+    <row r="926">
+      <c r="C926" s="123"/>
+      <c r="D926" s="124"/>
+    </row>
+    <row r="927">
+      <c r="C927" s="123"/>
+      <c r="D927" s="124"/>
+    </row>
+    <row r="928">
+      <c r="C928" s="123"/>
+      <c r="D928" s="124"/>
+    </row>
+    <row r="929">
+      <c r="C929" s="123"/>
+      <c r="D929" s="124"/>
+    </row>
+    <row r="930">
+      <c r="C930" s="123"/>
+      <c r="D930" s="124"/>
+    </row>
+    <row r="931">
+      <c r="C931" s="123"/>
+      <c r="D931" s="124"/>
+    </row>
+    <row r="932">
+      <c r="C932" s="123"/>
+      <c r="D932" s="124"/>
+    </row>
+    <row r="933">
+      <c r="C933" s="123"/>
+      <c r="D933" s="124"/>
+    </row>
+    <row r="934">
+      <c r="C934" s="123"/>
+      <c r="D934" s="124"/>
+    </row>
+    <row r="935">
+      <c r="C935" s="123"/>
+      <c r="D935" s="124"/>
+    </row>
+    <row r="936">
+      <c r="C936" s="123"/>
+      <c r="D936" s="124"/>
+    </row>
+    <row r="937">
+      <c r="C937" s="123"/>
+      <c r="D937" s="124"/>
+    </row>
+    <row r="938">
+      <c r="C938" s="123"/>
+      <c r="D938" s="124"/>
+    </row>
+    <row r="939">
+      <c r="C939" s="123"/>
+      <c r="D939" s="124"/>
+    </row>
+    <row r="940">
+      <c r="C940" s="123"/>
+      <c r="D940" s="124"/>
+    </row>
+    <row r="941">
+      <c r="C941" s="123"/>
+      <c r="D941" s="124"/>
+    </row>
+    <row r="942">
+      <c r="C942" s="123"/>
+      <c r="D942" s="124"/>
+    </row>
+    <row r="943">
+      <c r="C943" s="123"/>
+      <c r="D943" s="124"/>
+    </row>
+    <row r="944">
+      <c r="C944" s="123"/>
+      <c r="D944" s="124"/>
+    </row>
+    <row r="945">
+      <c r="C945" s="123"/>
+      <c r="D945" s="124"/>
+    </row>
+    <row r="946">
+      <c r="C946" s="123"/>
+      <c r="D946" s="124"/>
+    </row>
+    <row r="947">
+      <c r="C947" s="123"/>
+      <c r="D947" s="124"/>
+    </row>
+    <row r="948">
+      <c r="C948" s="123"/>
+      <c r="D948" s="124"/>
+    </row>
+    <row r="949">
+      <c r="C949" s="123"/>
+      <c r="D949" s="124"/>
+    </row>
+    <row r="950">
+      <c r="C950" s="123"/>
+      <c r="D950" s="124"/>
+    </row>
+    <row r="951">
+      <c r="C951" s="123"/>
+      <c r="D951" s="124"/>
+    </row>
+    <row r="952">
+      <c r="C952" s="123"/>
+      <c r="D952" s="124"/>
+    </row>
+    <row r="953">
+      <c r="C953" s="123"/>
+      <c r="D953" s="124"/>
+    </row>
+    <row r="954">
+      <c r="C954" s="123"/>
+      <c r="D954" s="124"/>
+    </row>
+    <row r="955">
+      <c r="C955" s="123"/>
+      <c r="D955" s="124"/>
+    </row>
+    <row r="956">
+      <c r="C956" s="123"/>
+      <c r="D956" s="124"/>
+    </row>
+    <row r="957">
+      <c r="C957" s="123"/>
+      <c r="D957" s="124"/>
+    </row>
+    <row r="958">
+      <c r="C958" s="123"/>
+      <c r="D958" s="124"/>
+    </row>
+    <row r="959">
+      <c r="C959" s="123"/>
+      <c r="D959" s="124"/>
+    </row>
+    <row r="960">
+      <c r="C960" s="123"/>
+      <c r="D960" s="124"/>
+    </row>
+    <row r="961">
+      <c r="C961" s="123"/>
+      <c r="D961" s="124"/>
+    </row>
+    <row r="962">
+      <c r="C962" s="123"/>
+      <c r="D962" s="124"/>
+    </row>
+    <row r="963">
+      <c r="C963" s="123"/>
+      <c r="D963" s="124"/>
+    </row>
+    <row r="964">
+      <c r="C964" s="123"/>
+      <c r="D964" s="124"/>
+    </row>
+    <row r="965">
+      <c r="C965" s="123"/>
+      <c r="D965" s="124"/>
+    </row>
+    <row r="966">
+      <c r="C966" s="123"/>
+      <c r="D966" s="124"/>
+    </row>
+    <row r="967">
+      <c r="C967" s="123"/>
+      <c r="D967" s="124"/>
+    </row>
+    <row r="968">
+      <c r="C968" s="123"/>
+      <c r="D968" s="124"/>
+    </row>
+    <row r="969">
+      <c r="C969" s="123"/>
+      <c r="D969" s="124"/>
+    </row>
+    <row r="970">
+      <c r="C970" s="123"/>
+      <c r="D970" s="124"/>
+    </row>
+    <row r="971">
+      <c r="C971" s="123"/>
+      <c r="D971" s="124"/>
+    </row>
+    <row r="972">
+      <c r="C972" s="123"/>
+      <c r="D972" s="124"/>
+    </row>
+    <row r="973">
+      <c r="C973" s="123"/>
+      <c r="D973" s="124"/>
+    </row>
+    <row r="974">
+      <c r="C974" s="123"/>
+      <c r="D974" s="124"/>
+    </row>
+    <row r="975">
+      <c r="C975" s="123"/>
+      <c r="D975" s="124"/>
+    </row>
+    <row r="976">
+      <c r="C976" s="123"/>
+      <c r="D976" s="124"/>
+    </row>
+    <row r="977">
+      <c r="C977" s="123"/>
+      <c r="D977" s="124"/>
+    </row>
+    <row r="978">
+      <c r="C978" s="123"/>
+      <c r="D978" s="124"/>
+    </row>
+    <row r="979">
+      <c r="C979" s="123"/>
+      <c r="D979" s="124"/>
+    </row>
+    <row r="980">
+      <c r="C980" s="123"/>
+      <c r="D980" s="124"/>
+    </row>
+    <row r="981">
+      <c r="C981" s="123"/>
+      <c r="D981" s="124"/>
+    </row>
+    <row r="982">
+      <c r="C982" s="123"/>
+      <c r="D982" s="124"/>
+    </row>
+    <row r="983">
+      <c r="C983" s="123"/>
+      <c r="D983" s="124"/>
+    </row>
+    <row r="984">
+      <c r="C984" s="123"/>
+      <c r="D984" s="124"/>
+    </row>
+    <row r="985">
+      <c r="C985" s="123"/>
+      <c r="D985" s="124"/>
+    </row>
+    <row r="986">
+      <c r="C986" s="123"/>
+      <c r="D986" s="124"/>
+    </row>
+    <row r="987">
+      <c r="C987" s="123"/>
+      <c r="D987" s="124"/>
+    </row>
+    <row r="988">
+      <c r="C988" s="123"/>
+      <c r="D988" s="124"/>
+    </row>
+    <row r="989">
+      <c r="C989" s="123"/>
+      <c r="D989" s="124"/>
+    </row>
+    <row r="990">
+      <c r="C990" s="123"/>
+      <c r="D990" s="124"/>
+    </row>
+    <row r="991">
+      <c r="C991" s="123"/>
+      <c r="D991" s="124"/>
+    </row>
+    <row r="992">
+      <c r="C992" s="123"/>
+      <c r="D992" s="124"/>
+    </row>
+    <row r="993">
+      <c r="C993" s="123"/>
+      <c r="D993" s="124"/>
+    </row>
+    <row r="994">
+      <c r="C994" s="123"/>
+      <c r="D994" s="124"/>
+    </row>
+    <row r="995">
+      <c r="C995" s="123"/>
+      <c r="D995" s="124"/>
+    </row>
+    <row r="996">
+      <c r="C996" s="123"/>
+      <c r="D996" s="124"/>
+    </row>
+    <row r="997">
+      <c r="C997" s="123"/>
+      <c r="D997" s="124"/>
+    </row>
+    <row r="998">
+      <c r="C998" s="123"/>
+      <c r="D998" s="124"/>
+    </row>
+    <row r="999">
+      <c r="C999" s="123"/>
+      <c r="D999" s="124"/>
+    </row>
+    <row r="1000">
+      <c r="C1000" s="123"/>
+      <c r="D1000" s="124"/>
+    </row>
+    <row r="1001">
+      <c r="C1001" s="123"/>
+      <c r="D1001" s="124"/>
+    </row>
+    <row r="1002">
+      <c r="C1002" s="123"/>
+      <c r="D1002" s="124"/>
+    </row>
+    <row r="1003">
+      <c r="C1003" s="123"/>
+      <c r="D1003" s="124"/>
+    </row>
+    <row r="1004">
+      <c r="C1004" s="123"/>
+      <c r="D1004" s="124"/>
+    </row>
+    <row r="1005">
+      <c r="C1005" s="123"/>
+      <c r="D1005" s="124"/>
+    </row>
+    <row r="1006">
+      <c r="C1006" s="123"/>
+      <c r="D1006" s="124"/>
+    </row>
+    <row r="1007">
+      <c r="C1007" s="123"/>
+      <c r="D1007" s="124"/>
+    </row>
+    <row r="1008">
+      <c r="C1008" s="123"/>
+      <c r="D1008" s="124"/>
+    </row>
+    <row r="1009">
+      <c r="C1009" s="123"/>
+      <c r="D1009" s="124"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="C11:C20"/>
+    <mergeCell ref="D11:D20"/>
+    <mergeCell ref="D21:D30"/>
+    <mergeCell ref="E35:E39"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A11:A30"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="C50:D52"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="B21:B30"/>
+    <mergeCell ref="C21:C30"/>
+    <mergeCell ref="A32:A44"/>
+    <mergeCell ref="B32:B39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A45:A61"/>
+    <mergeCell ref="B53:B61"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
